--- a/testFiles/SoilWaterContent.xlsx
+++ b/testFiles/SoilWaterContent.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creagov-my.sharepoint.com/personal/simoneugomaria_bregaglio_crea_gov_it/Documents/Desktop/model dev/cumba/cumba_R_package/testFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="10_ncr:100000_{5A7756DC-657B-435E-BDEB-7295ED461E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D7A20A3-D1A4-427A-AC6A-32C9F6767538}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="10_ncr:100000_{5A7756DC-657B-435E-BDEB-7295ED461E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A90A67-8354-40F0-92A3-2016002A6CAE}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2748" yWindow="3288" windowWidth="17280" windowHeight="9984" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -581,2249 +581,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Foglio1!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>SWC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>Foglio1!$E$2:$E$452</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="451"/>
-                <c:pt idx="0">
-                  <c:v>35.611257139999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>35.921441665000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>35.955710420000003</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>36.297966664999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>38.684260414999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>36.439427080000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>36.229583335000001</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>36.082099999999997</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>36.033306249999995</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36.006302085000002</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>35.905041664999999</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>35.756874999999994</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>35.666428569999994</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>35.474166664999998</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>35.720641665000002</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>35.977812499999999</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>36.006581249999996</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>36.310970834999999</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>36.163297920000005</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>36.060622914999996</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>35.737793749999994</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>35.731041669999996</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>35.608939579999998</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>35.474635419999998</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>35.484843750000003</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>35.702608694999995</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>35.403993749999998</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>35.552831249999997</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>35.828870835000004</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>35.036043750000005</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>33.397154165000003</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>33.260552085</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>33.975872914999997</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>32.736981249999999</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>32.757489585000002</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>33.673349999999999</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>33.329533335000001</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>32.118124999999999</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>31.873402079999998</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>33.464879164999999</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>31.909322914999997</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>32.123645835000005</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>33.558141669999998</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>32.262639579999998</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>30.907431250000002</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>31.199858335000002</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>33.22677083</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>33.192245649999997</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>33.070468750000003</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>32.841475000000003</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>32.907308335000003</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>31.423169565000002</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>31.694582610000001</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>33.21821739</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>33.222672914999997</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>33.153089585000004</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>33.338191664999997</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>33.502552080000001</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>32.255364580000006</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>32.318913039999998</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>32.630661764999999</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>32.640279164999995</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>32.660833330000003</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>32.693802085000002</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>32.822933335000002</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>30.980812499999999</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>30.704547914999999</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>31.704062499999999</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>30.985433335</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>31.045954164999998</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>29.488454165</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>30.165954165000002</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>29.1649125</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>27.621024999999999</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>26.620433335000001</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>27.325879999999998</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>26.688108334999999</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>26.258472914999999</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>26.600660415</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>25.89015625</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>25.30828125</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>25.138679170000003</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>25.019027080000001</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>24.744089580000001</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>24.411060419999998</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>24.093072915</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>23.810208334999999</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>23.598177085000003</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>23.42921875</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>23.28538125</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>23.179410415</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>23.098870830000003</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>23.049047914999999</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>23.02071042</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>23.000104165</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>35.661485714999998</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>35.740293749999999</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>35.678785415</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>36.316597915000003</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>39.67890208</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>37.685016669999996</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>37.246702084999995</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>36.993227079999997</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>36.821893750000001</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>36.748135415</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>36.724583335000005</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>36.673602944999999</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>36.618461539999998</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>36.514375000000001</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>37.117368749999997</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>37.322516664999995</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>37.45439167</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>37.426789580000005</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>37.047777080000003</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>36.825666665</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>36.661041664999999</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>36.674183330000005</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>36.477674999999998</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>36.358166664999999</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>36.734479164999996</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>37.082826085000001</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>36.564860420000002</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>37.147760419999997</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>37.484391665000004</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>36.79265625</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>35.5720125</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>36.903171740000005</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>37.368820835000001</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>35.979708329999994</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>36.202241665000003</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>37.053110414999999</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>36.489322915000002</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>34.814860414999998</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>35.155345835000006</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>38.165625000000006</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>36.392793749999996</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>36.449929170000004</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>38.504495835</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>37.675520829999996</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>35.865625000000001</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>35.602031249999996</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>37.106493749999998</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>38.405523909999999</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>38.067656249999999</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>38.097135414999997</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>37.843612499999999</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>35.665978260000003</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>35.101717395000001</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>36.000091304999998</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>36.723297915000003</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>35.931145834999995</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>36.550535414999999</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>36.878462499999998</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>35.234252085000001</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>36.337952170000001</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>36.452329415000001</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>37.194512500000002</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>37.015764584999999</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>37.150693750000002</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>36.580279165</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>34.399304165000004</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>35.5215125</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>37.076214585000002</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>37.761372914999995</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>37.664739580000003</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>38.682795835</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>38.140593750000001</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>36.503333330000004</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>35.173558334999996</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>37.059739585000003</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>38.397374999999997</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>36.938506250000003</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>37.489177085000001</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>38.456389584999997</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>37.091652080000003</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>37.197987499999996</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>38.318837500000001</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>37.428318750000003</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>36.472172915000002</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>35.359270835000004</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>33.79243125</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>31.9542875</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>30.140641670000001</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>28.4892</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>27.4386625</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>27.26095625</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>27.132764585</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>26.865450000000003</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>26.632708335</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>26.318662500000002</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>38.50486111</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>38.818835419999999</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>39.44848958</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>39.353785420000001</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>39.036958329999997</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>38.477743750000002</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>38.459166670000002</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>38.786354170000003</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>38.897760419999997</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>38.85430625</c:v>
-                </c:pt>
-                <c:pt idx="200">
-                  <c:v>38.988595830000001</c:v>
-                </c:pt>
-                <c:pt idx="201">
-                  <c:v>39.020106249999998</c:v>
-                </c:pt>
-                <c:pt idx="202">
-                  <c:v>39.254056669999997</c:v>
-                </c:pt>
-                <c:pt idx="203">
-                  <c:v>39.976428570000003</c:v>
-                </c:pt>
-                <c:pt idx="204">
-                  <c:v>39.957935419999998</c:v>
-                </c:pt>
-                <c:pt idx="205">
-                  <c:v>40.11982708</c:v>
-                </c:pt>
-                <c:pt idx="206">
-                  <c:v>40.564877080000002</c:v>
-                </c:pt>
-                <c:pt idx="207">
-                  <c:v>40.762519050000002</c:v>
-                </c:pt>
-                <c:pt idx="208">
-                  <c:v>43.51267</c:v>
-                </c:pt>
-                <c:pt idx="209">
-                  <c:v>42.44678571</c:v>
-                </c:pt>
-                <c:pt idx="210">
-                  <c:v>42.061668179999998</c:v>
-                </c:pt>
-                <c:pt idx="211">
-                  <c:v>43.051949999999998</c:v>
-                </c:pt>
-                <c:pt idx="212">
-                  <c:v>42.944312500000002</c:v>
-                </c:pt>
-                <c:pt idx="213">
-                  <c:v>42.098042499999998</c:v>
-                </c:pt>
-                <c:pt idx="214">
-                  <c:v>41.074832499999999</c:v>
-                </c:pt>
-                <c:pt idx="215">
-                  <c:v>42.163145450000002</c:v>
-                </c:pt>
-                <c:pt idx="216">
-                  <c:v>42.523405259999997</c:v>
-                </c:pt>
-                <c:pt idx="217">
-                  <c:v>41.309708819999997</c:v>
-                </c:pt>
-                <c:pt idx="218">
-                  <c:v>42.363900000000001</c:v>
-                </c:pt>
-                <c:pt idx="219">
-                  <c:v>42.374747370000001</c:v>
-                </c:pt>
-                <c:pt idx="220">
-                  <c:v>41.289527499999998</c:v>
-                </c:pt>
-                <c:pt idx="221">
-                  <c:v>40.452647059999997</c:v>
-                </c:pt>
-                <c:pt idx="222">
-                  <c:v>39.440093179999998</c:v>
-                </c:pt>
-                <c:pt idx="223">
-                  <c:v>38.287047919999999</c:v>
-                </c:pt>
-                <c:pt idx="224">
-                  <c:v>40.241370830000001</c:v>
-                </c:pt>
-                <c:pt idx="225">
-                  <c:v>42.390875000000001</c:v>
-                </c:pt>
-                <c:pt idx="226">
-                  <c:v>40.893233330000001</c:v>
-                </c:pt>
-                <c:pt idx="227">
-                  <c:v>40.177185420000001</c:v>
-                </c:pt>
-                <c:pt idx="228">
-                  <c:v>39.774360420000001</c:v>
-                </c:pt>
-                <c:pt idx="229">
-                  <c:v>39.32453125</c:v>
-                </c:pt>
-                <c:pt idx="230">
-                  <c:v>40.977849999999997</c:v>
-                </c:pt>
-                <c:pt idx="231">
-                  <c:v>41.562047919999998</c:v>
-                </c:pt>
-                <c:pt idx="232">
-                  <c:v>40.709635419999998</c:v>
-                </c:pt>
-                <c:pt idx="233">
-                  <c:v>40.6347375</c:v>
-                </c:pt>
-                <c:pt idx="234">
-                  <c:v>39.867258329999999</c:v>
-                </c:pt>
-                <c:pt idx="235">
-                  <c:v>39.152308329999997</c:v>
-                </c:pt>
-                <c:pt idx="236">
-                  <c:v>40.21368125</c:v>
-                </c:pt>
-                <c:pt idx="237">
-                  <c:v>41.11743542</c:v>
-                </c:pt>
-                <c:pt idx="238">
-                  <c:v>41.85220417</c:v>
-                </c:pt>
-                <c:pt idx="239">
-                  <c:v>41.557135420000002</c:v>
-                </c:pt>
-                <c:pt idx="240">
-                  <c:v>40.712150000000001</c:v>
-                </c:pt>
-                <c:pt idx="241">
-                  <c:v>40.261304170000003</c:v>
-                </c:pt>
-                <c:pt idx="242">
-                  <c:v>42.044116670000001</c:v>
-                </c:pt>
-                <c:pt idx="243">
-                  <c:v>42.699545829999998</c:v>
-                </c:pt>
-                <c:pt idx="244">
-                  <c:v>43.446245830000002</c:v>
-                </c:pt>
-                <c:pt idx="245">
-                  <c:v>43.049799999999998</c:v>
-                </c:pt>
-                <c:pt idx="246">
-                  <c:v>43.39211667</c:v>
-                </c:pt>
-                <c:pt idx="247">
-                  <c:v>43.11012083</c:v>
-                </c:pt>
-                <c:pt idx="248">
-                  <c:v>41.735439579999998</c:v>
-                </c:pt>
-                <c:pt idx="249">
-                  <c:v>42.299947920000001</c:v>
-                </c:pt>
-                <c:pt idx="250">
-                  <c:v>42.471195829999999</c:v>
-                </c:pt>
-                <c:pt idx="251">
-                  <c:v>42.804099999999998</c:v>
-                </c:pt>
-                <c:pt idx="252">
-                  <c:v>42.653125000000003</c:v>
-                </c:pt>
-                <c:pt idx="253">
-                  <c:v>43.447256250000002</c:v>
-                </c:pt>
-                <c:pt idx="254">
-                  <c:v>43.08128542</c:v>
-                </c:pt>
-                <c:pt idx="255">
-                  <c:v>42.131720829999999</c:v>
-                </c:pt>
-                <c:pt idx="256">
-                  <c:v>41.4729375</c:v>
-                </c:pt>
-                <c:pt idx="257">
-                  <c:v>41.00368125</c:v>
-                </c:pt>
-                <c:pt idx="258">
-                  <c:v>41.661564579999997</c:v>
-                </c:pt>
-                <c:pt idx="259">
-                  <c:v>41.894539469999998</c:v>
-                </c:pt>
-                <c:pt idx="260">
-                  <c:v>42.49291667</c:v>
-                </c:pt>
-                <c:pt idx="261">
-                  <c:v>42.72170208</c:v>
-                </c:pt>
-                <c:pt idx="262">
-                  <c:v>41.770625000000003</c:v>
-                </c:pt>
-                <c:pt idx="263">
-                  <c:v>42.263627079999999</c:v>
-                </c:pt>
-                <c:pt idx="264">
-                  <c:v>42.627047920000003</c:v>
-                </c:pt>
-                <c:pt idx="265">
-                  <c:v>41.705089579999999</c:v>
-                </c:pt>
-                <c:pt idx="266">
-                  <c:v>40.992258329999999</c:v>
-                </c:pt>
-                <c:pt idx="267">
-                  <c:v>40.239212500000001</c:v>
-                </c:pt>
-                <c:pt idx="268">
-                  <c:v>39.422239580000003</c:v>
-                </c:pt>
-                <c:pt idx="269">
-                  <c:v>38.547033329999998</c:v>
-                </c:pt>
-                <c:pt idx="270">
-                  <c:v>37.558889579999999</c:v>
-                </c:pt>
-                <c:pt idx="271">
-                  <c:v>36.151291669999999</c:v>
-                </c:pt>
-                <c:pt idx="272">
-                  <c:v>34.342708330000001</c:v>
-                </c:pt>
-                <c:pt idx="273">
-                  <c:v>32.055622919999998</c:v>
-                </c:pt>
-                <c:pt idx="274">
-                  <c:v>30.649643749999999</c:v>
-                </c:pt>
-                <c:pt idx="275">
-                  <c:v>30.015379169999999</c:v>
-                </c:pt>
-                <c:pt idx="276">
-                  <c:v>29.389184090000001</c:v>
-                </c:pt>
-                <c:pt idx="277">
-                  <c:v>40.650927777777774</c:v>
-                </c:pt>
-                <c:pt idx="278">
-                  <c:v>41.047499999999985</c:v>
-                </c:pt>
-                <c:pt idx="279">
-                  <c:v>41.69001875</c:v>
-                </c:pt>
-                <c:pt idx="280">
-                  <c:v>41.609931249999995</c:v>
-                </c:pt>
-                <c:pt idx="281">
-                  <c:v>41.40442083333334</c:v>
-                </c:pt>
-                <c:pt idx="282">
-                  <c:v>40.656162500000001</c:v>
-                </c:pt>
-                <c:pt idx="283">
-                  <c:v>40.577152083333331</c:v>
-                </c:pt>
-                <c:pt idx="284">
-                  <c:v>40.905935416666672</c:v>
-                </c:pt>
-                <c:pt idx="285">
-                  <c:v>41.059912500000003</c:v>
-                </c:pt>
-                <c:pt idx="286">
-                  <c:v>41.17557291666666</c:v>
-                </c:pt>
-                <c:pt idx="287">
-                  <c:v>41.375222916666665</c:v>
-                </c:pt>
-                <c:pt idx="288">
-                  <c:v>41.464966666666669</c:v>
-                </c:pt>
-                <c:pt idx="289">
-                  <c:v>41.778416666666665</c:v>
-                </c:pt>
-                <c:pt idx="290">
-                  <c:v>42.770364285714287</c:v>
-                </c:pt>
-                <c:pt idx="291">
-                  <c:v>42.708595833333334</c:v>
-                </c:pt>
-                <c:pt idx="292">
-                  <c:v>42.831929166666662</c:v>
-                </c:pt>
-                <c:pt idx="293">
-                  <c:v>42.881181250000004</c:v>
-                </c:pt>
-                <c:pt idx="294">
-                  <c:v>42.724082499999994</c:v>
-                </c:pt>
-                <c:pt idx="295">
-                  <c:v>43.692991666666671</c:v>
-                </c:pt>
-                <c:pt idx="296">
-                  <c:v>43.788199999999996</c:v>
-                </c:pt>
-                <c:pt idx="297">
-                  <c:v>43.690202380952378</c:v>
-                </c:pt>
-                <c:pt idx="298">
-                  <c:v>43.930244736842099</c:v>
-                </c:pt>
-                <c:pt idx="299">
-                  <c:v>44.136884999999999</c:v>
-                </c:pt>
-                <c:pt idx="300">
-                  <c:v>43.441457499999991</c:v>
-                </c:pt>
-                <c:pt idx="301">
-                  <c:v>41.309562499999991</c:v>
-                </c:pt>
-                <c:pt idx="302">
-                  <c:v>40.59755454545455</c:v>
-                </c:pt>
-                <c:pt idx="303">
-                  <c:v>41.987449999999995</c:v>
-                </c:pt>
-                <c:pt idx="304">
-                  <c:v>39.344897058823534</c:v>
-                </c:pt>
-                <c:pt idx="305">
-                  <c:v>41.283935</c:v>
-                </c:pt>
-                <c:pt idx="306">
-                  <c:v>45.289013157894722</c:v>
-                </c:pt>
-                <c:pt idx="307">
-                  <c:v>44.087687500000001</c:v>
-                </c:pt>
-                <c:pt idx="308">
-                  <c:v>42.967155882352948</c:v>
-                </c:pt>
-                <c:pt idx="309">
-                  <c:v>40.781477272727265</c:v>
-                </c:pt>
-                <c:pt idx="310">
-                  <c:v>38.044947916666679</c:v>
-                </c:pt>
-                <c:pt idx="311">
-                  <c:v>39.930695833333338</c:v>
-                </c:pt>
-                <c:pt idx="312">
-                  <c:v>43.071042500000004</c:v>
-                </c:pt>
-                <c:pt idx="313">
-                  <c:v>41.284220833333336</c:v>
-                </c:pt>
-                <c:pt idx="314">
-                  <c:v>40.396162499999996</c:v>
-                </c:pt>
-                <c:pt idx="315">
-                  <c:v>39.649014583333326</c:v>
-                </c:pt>
-                <c:pt idx="316">
-                  <c:v>38.624235416666671</c:v>
-                </c:pt>
-                <c:pt idx="317">
-                  <c:v>40.130850000000002</c:v>
-                </c:pt>
-                <c:pt idx="318">
-                  <c:v>40.892031249999995</c:v>
-                </c:pt>
-                <c:pt idx="319">
-                  <c:v>39.834895833333327</c:v>
-                </c:pt>
-                <c:pt idx="320">
-                  <c:v>39.614008333333338</c:v>
-                </c:pt>
-                <c:pt idx="321">
-                  <c:v>38.565970833333331</c:v>
-                </c:pt>
-                <c:pt idx="322">
-                  <c:v>37.45817916666666</c:v>
-                </c:pt>
-                <c:pt idx="323">
-                  <c:v>38.100518750000006</c:v>
-                </c:pt>
-                <c:pt idx="324">
-                  <c:v>38.857658333333326</c:v>
-                </c:pt>
-                <c:pt idx="325">
-                  <c:v>40.107954166666666</c:v>
-                </c:pt>
-                <c:pt idx="326">
-                  <c:v>40.295762500000002</c:v>
-                </c:pt>
-                <c:pt idx="327">
-                  <c:v>38.987212500000005</c:v>
-                </c:pt>
-                <c:pt idx="328">
-                  <c:v>38.121416666666654</c:v>
-                </c:pt>
-                <c:pt idx="329">
-                  <c:v>40.494114583333342</c:v>
-                </c:pt>
-                <c:pt idx="330">
-                  <c:v>41.521456250000007</c:v>
-                </c:pt>
-                <c:pt idx="331">
-                  <c:v>41.320939583333335</c:v>
-                </c:pt>
-                <c:pt idx="332">
-                  <c:v>40.903390909090916</c:v>
-                </c:pt>
-                <c:pt idx="333">
-                  <c:v>41.556806249999994</c:v>
-                </c:pt>
-                <c:pt idx="334">
-                  <c:v>41.487068749999985</c:v>
-                </c:pt>
-                <c:pt idx="335">
-                  <c:v>40.106562499999995</c:v>
-                </c:pt>
-                <c:pt idx="336">
-                  <c:v>40.912622916666663</c:v>
-                </c:pt>
-                <c:pt idx="337">
-                  <c:v>41.050587499999999</c:v>
-                </c:pt>
-                <c:pt idx="338">
-                  <c:v>41.461433333333332</c:v>
-                </c:pt>
-                <c:pt idx="339">
-                  <c:v>41.316927083333333</c:v>
-                </c:pt>
-                <c:pt idx="340">
-                  <c:v>42.214706249999999</c:v>
-                </c:pt>
-                <c:pt idx="341">
-                  <c:v>41.724706250000004</c:v>
-                </c:pt>
-                <c:pt idx="342">
-                  <c:v>40.550508333333326</c:v>
-                </c:pt>
-                <c:pt idx="343">
-                  <c:v>39.657872499999996</c:v>
-                </c:pt>
-                <c:pt idx="344">
-                  <c:v>39.038333333333334</c:v>
-                </c:pt>
-                <c:pt idx="345">
-                  <c:v>39.737516666666664</c:v>
-                </c:pt>
-                <c:pt idx="346">
-                  <c:v>39.826684210526317</c:v>
-                </c:pt>
-                <c:pt idx="347">
-                  <c:v>41.034704166666664</c:v>
-                </c:pt>
-                <c:pt idx="348">
-                  <c:v>41.426093750000007</c:v>
-                </c:pt>
-                <c:pt idx="349">
-                  <c:v>40.133804166666678</c:v>
-                </c:pt>
-                <c:pt idx="350">
-                  <c:v>40.283127083333333</c:v>
-                </c:pt>
-                <c:pt idx="351">
-                  <c:v>40.736441666666671</c:v>
-                </c:pt>
-                <c:pt idx="352">
-                  <c:v>39.704927083333331</c:v>
-                </c:pt>
-                <c:pt idx="353">
-                  <c:v>38.572920833333335</c:v>
-                </c:pt>
-                <c:pt idx="354">
-                  <c:v>36.853506250000002</c:v>
-                </c:pt>
-                <c:pt idx="355">
-                  <c:v>34.042012499999991</c:v>
-                </c:pt>
-                <c:pt idx="356">
-                  <c:v>31.083460416666668</c:v>
-                </c:pt>
-                <c:pt idx="357">
-                  <c:v>28.825729166666665</c:v>
-                </c:pt>
-                <c:pt idx="358">
-                  <c:v>27.386275000000001</c:v>
-                </c:pt>
-                <c:pt idx="359">
-                  <c:v>26.241041666666661</c:v>
-                </c:pt>
-                <c:pt idx="360">
-                  <c:v>25.3863375</c:v>
-                </c:pt>
-                <c:pt idx="361">
-                  <c:v>24.923489583333335</c:v>
-                </c:pt>
-                <c:pt idx="362">
-                  <c:v>24.503662500000001</c:v>
-                </c:pt>
-                <c:pt idx="363">
-                  <c:v>24.220284090909093</c:v>
-                </c:pt>
-                <c:pt idx="364">
-                  <c:v>41.510972222222222</c:v>
-                </c:pt>
-                <c:pt idx="365">
-                  <c:v>41.959254166666661</c:v>
-                </c:pt>
-                <c:pt idx="366">
-                  <c:v>42.261266666666664</c:v>
-                </c:pt>
-                <c:pt idx="367">
-                  <c:v>42.507412500000001</c:v>
-                </c:pt>
-                <c:pt idx="368">
-                  <c:v>42.257554166666665</c:v>
-                </c:pt>
-                <c:pt idx="369">
-                  <c:v>41.507310416666662</c:v>
-                </c:pt>
-                <c:pt idx="370">
-                  <c:v>41.504774999999988</c:v>
-                </c:pt>
-                <c:pt idx="371">
-                  <c:v>41.831006249999994</c:v>
-                </c:pt>
-                <c:pt idx="372">
-                  <c:v>42.062902083333334</c:v>
-                </c:pt>
-                <c:pt idx="373">
-                  <c:v>42.12088541666666</c:v>
-                </c:pt>
-                <c:pt idx="374">
-                  <c:v>42.116454166666678</c:v>
-                </c:pt>
-                <c:pt idx="375">
-                  <c:v>41.68831458333333</c:v>
-                </c:pt>
-                <c:pt idx="376">
-                  <c:v>41.494635714285714</c:v>
-                </c:pt>
-                <c:pt idx="377">
-                  <c:v>42.487021428571431</c:v>
-                </c:pt>
-                <c:pt idx="378">
-                  <c:v>42.729029166666663</c:v>
-                </c:pt>
-                <c:pt idx="379">
-                  <c:v>42.974843750000012</c:v>
-                </c:pt>
-                <c:pt idx="380">
-                  <c:v>43.361562499999991</c:v>
-                </c:pt>
-                <c:pt idx="381">
-                  <c:v>43.530752380952379</c:v>
-                </c:pt>
-                <c:pt idx="382">
-                  <c:v>43.693214285714284</c:v>
-                </c:pt>
-                <c:pt idx="383">
-                  <c:v>43.472710714285711</c:v>
-                </c:pt>
-                <c:pt idx="384">
-                  <c:v>43.174980000000005</c:v>
-                </c:pt>
-                <c:pt idx="385">
-                  <c:v>42.811390476190475</c:v>
-                </c:pt>
-                <c:pt idx="386">
-                  <c:v>42.446414999999995</c:v>
-                </c:pt>
-                <c:pt idx="387">
-                  <c:v>41.877272500000004</c:v>
-                </c:pt>
-                <c:pt idx="388">
-                  <c:v>41.083562500000006</c:v>
-                </c:pt>
-                <c:pt idx="389">
-                  <c:v>39.908275000000003</c:v>
-                </c:pt>
-                <c:pt idx="390">
-                  <c:v>38.772549999999995</c:v>
-                </c:pt>
-                <c:pt idx="391">
-                  <c:v>37.392376470588232</c:v>
-                </c:pt>
-                <c:pt idx="392">
-                  <c:v>37.843442105263158</c:v>
-                </c:pt>
-                <c:pt idx="393">
-                  <c:v>43.32203684210527</c:v>
-                </c:pt>
-                <c:pt idx="394">
-                  <c:v>42.589812500000008</c:v>
-                </c:pt>
-                <c:pt idx="395">
-                  <c:v>41.960541176470585</c:v>
-                </c:pt>
-                <c:pt idx="396">
-                  <c:v>41.050815909090907</c:v>
-                </c:pt>
-                <c:pt idx="397">
-                  <c:v>39.999235416666671</c:v>
-                </c:pt>
-                <c:pt idx="398">
-                  <c:v>39.066231250000008</c:v>
-                </c:pt>
-                <c:pt idx="399">
-                  <c:v>41.981517499999988</c:v>
-                </c:pt>
-                <c:pt idx="400">
-                  <c:v>41.82480833333333</c:v>
-                </c:pt>
-                <c:pt idx="401">
-                  <c:v>41.156995833333333</c:v>
-                </c:pt>
-                <c:pt idx="402">
-                  <c:v>40.488139583333336</c:v>
-                </c:pt>
-                <c:pt idx="403">
-                  <c:v>39.788574999999994</c:v>
-                </c:pt>
-                <c:pt idx="404">
-                  <c:v>39.633997916666658</c:v>
-                </c:pt>
-                <c:pt idx="405">
-                  <c:v>39.808925000000002</c:v>
-                </c:pt>
-                <c:pt idx="406">
-                  <c:v>39.024985416666667</c:v>
-                </c:pt>
-                <c:pt idx="407">
-                  <c:v>38.122287499999992</c:v>
-                </c:pt>
-                <c:pt idx="408">
-                  <c:v>37.540831249999989</c:v>
-                </c:pt>
-                <c:pt idx="409">
-                  <c:v>36.611650000000004</c:v>
-                </c:pt>
-                <c:pt idx="410">
-                  <c:v>35.42160208333334</c:v>
-                </c:pt>
-                <c:pt idx="411">
-                  <c:v>34.16530208333333</c:v>
-                </c:pt>
-                <c:pt idx="412">
-                  <c:v>32.812879166666669</c:v>
-                </c:pt>
-                <c:pt idx="413">
-                  <c:v>31.876722916666665</c:v>
-                </c:pt>
-                <c:pt idx="414">
-                  <c:v>31.026891666666671</c:v>
-                </c:pt>
-                <c:pt idx="415">
-                  <c:v>30.523733333333329</c:v>
-                </c:pt>
-                <c:pt idx="416">
-                  <c:v>29.938385416666662</c:v>
-                </c:pt>
-                <c:pt idx="417">
-                  <c:v>29.378872916666669</c:v>
-                </c:pt>
-                <c:pt idx="418">
-                  <c:v>28.928956249999999</c:v>
-                </c:pt>
-                <c:pt idx="419">
-                  <c:v>28.744836956521741</c:v>
-                </c:pt>
-                <c:pt idx="420">
-                  <c:v>28.536372916666668</c:v>
-                </c:pt>
-                <c:pt idx="421">
-                  <c:v>28.116564583333329</c:v>
-                </c:pt>
-                <c:pt idx="422">
-                  <c:v>27.666866666666674</c:v>
-                </c:pt>
-                <c:pt idx="423">
-                  <c:v>27.194014583333331</c:v>
-                </c:pt>
-                <c:pt idx="424">
-                  <c:v>26.823718750000001</c:v>
-                </c:pt>
-                <c:pt idx="425">
-                  <c:v>26.598405555555559</c:v>
-                </c:pt>
-                <c:pt idx="426">
-                  <c:v>26.488768750000002</c:v>
-                </c:pt>
-                <c:pt idx="427">
-                  <c:v>26.512947916666665</c:v>
-                </c:pt>
-                <c:pt idx="428">
-                  <c:v>26.446662499999999</c:v>
-                </c:pt>
-                <c:pt idx="429">
-                  <c:v>26.306608333333333</c:v>
-                </c:pt>
-                <c:pt idx="430">
-                  <c:v>26.141222499999998</c:v>
-                </c:pt>
-                <c:pt idx="431">
-                  <c:v>25.785920833333336</c:v>
-                </c:pt>
-                <c:pt idx="432">
-                  <c:v>25.383822916666663</c:v>
-                </c:pt>
-                <c:pt idx="433">
-                  <c:v>25.217963157894733</c:v>
-                </c:pt>
-                <c:pt idx="434">
-                  <c:v>25.157114583333339</c:v>
-                </c:pt>
-                <c:pt idx="435">
-                  <c:v>25.159252083333339</c:v>
-                </c:pt>
-                <c:pt idx="436">
-                  <c:v>25.167777083333334</c:v>
-                </c:pt>
-                <c:pt idx="437">
-                  <c:v>25.159293478260871</c:v>
-                </c:pt>
-                <c:pt idx="438">
-                  <c:v>24.671093749999997</c:v>
-                </c:pt>
-                <c:pt idx="439">
-                  <c:v>24.390345833333338</c:v>
-                </c:pt>
-                <c:pt idx="440">
-                  <c:v>24.298504166666664</c:v>
-                </c:pt>
-                <c:pt idx="441">
-                  <c:v>24.33663125</c:v>
-                </c:pt>
-                <c:pt idx="442">
-                  <c:v>24.409877083333328</c:v>
-                </c:pt>
-                <c:pt idx="443">
-                  <c:v>24.529449999999997</c:v>
-                </c:pt>
-                <c:pt idx="444">
-                  <c:v>24.511927083333337</c:v>
-                </c:pt>
-                <c:pt idx="445">
-                  <c:v>24.478690909090911</c:v>
-                </c:pt>
-                <c:pt idx="446">
-                  <c:v>24.439062500000002</c:v>
-                </c:pt>
-                <c:pt idx="447">
-                  <c:v>24.387152083333334</c:v>
-                </c:pt>
-                <c:pt idx="448">
-                  <c:v>24.336649999999995</c:v>
-                </c:pt>
-                <c:pt idx="449">
-                  <c:v>24.247795833333331</c:v>
-                </c:pt>
-                <c:pt idx="450">
-                  <c:v>24.150681818181816</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FB76-4889-B462-F608B9591672}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="250107871"/>
-        <c:axId val="250115551"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="250107871"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="250115551"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="250115551"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="250107871"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>316773</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>9253</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>113210</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>9253</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD61571F-1235-41D3-EE07-950B81AEEC72}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3111,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E452"/>
+  <dimension ref="A1:E386"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
@@ -3145,10 +902,10 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>35.611257139999999</v>
+        <v>38.684260414999997</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3162,10 +919,10 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>35.921441665000003</v>
+        <v>36.439427080000002</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3179,10 +936,10 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>35.955710420000003</v>
+        <v>36.229583335000001</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3196,10 +953,10 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>36.297966664999997</v>
+        <v>36.082099999999997</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3213,10 +970,10 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>38.684260414999997</v>
+        <v>36.033306249999995</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3230,10 +987,10 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>36.439427080000002</v>
+        <v>36.006302085000002</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3247,10 +1004,10 @@
         <v>5</v>
       </c>
       <c r="D8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>36.229583335000001</v>
+        <v>35.905041664999999</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3264,10 +1021,10 @@
         <v>5</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>36.082099999999997</v>
+        <v>35.756874999999994</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3281,10 +1038,10 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E10">
-        <v>36.033306249999995</v>
+        <v>35.666428569999994</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3298,10 +1055,10 @@
         <v>5</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E11">
-        <v>36.006302085000002</v>
+        <v>35.474166664999998</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3315,10 +1072,10 @@
         <v>5</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E12">
-        <v>35.905041664999999</v>
+        <v>35.720641665000002</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3332,10 +1089,10 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E13">
-        <v>35.756874999999994</v>
+        <v>35.977812499999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3349,10 +1106,10 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E14">
-        <v>35.666428569999994</v>
+        <v>36.006581249999996</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3366,10 +1123,10 @@
         <v>5</v>
       </c>
       <c r="D15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>35.474166664999998</v>
+        <v>36.310970834999999</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3383,10 +1140,10 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E16">
-        <v>35.720641665000002</v>
+        <v>36.163297920000005</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3400,10 +1157,10 @@
         <v>5</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>35.977812499999999</v>
+        <v>36.060622914999996</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3417,10 +1174,10 @@
         <v>5</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E18">
-        <v>36.006581249999996</v>
+        <v>35.737793749999994</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3434,10 +1191,10 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E19">
-        <v>36.310970834999999</v>
+        <v>35.731041669999996</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3451,10 +1208,10 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20">
-        <v>36.163297920000005</v>
+        <v>35.608939579999998</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3468,10 +1225,10 @@
         <v>5</v>
       </c>
       <c r="D21">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E21">
-        <v>36.060622914999996</v>
+        <v>35.474635419999998</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3485,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E22">
-        <v>35.737793749999994</v>
+        <v>35.484843750000003</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3502,10 +1259,10 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E23">
-        <v>35.731041669999996</v>
+        <v>35.702608694999995</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3519,10 +1276,10 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E24">
-        <v>35.608939579999998</v>
+        <v>35.403993749999998</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3533,13 +1290,13 @@
         <v>2017</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>35.474635419999998</v>
+        <v>35.552831249999997</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3550,13 +1307,13 @@
         <v>2017</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>35.484843750000003</v>
+        <v>35.828870835000004</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3567,13 +1324,13 @@
         <v>2017</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>35.702608694999995</v>
+        <v>35.036043750000005</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3584,13 +1341,13 @@
         <v>2017</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E28">
-        <v>35.403993749999998</v>
+        <v>33.397154165000003</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3604,10 +1361,10 @@
         <v>6</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29">
-        <v>35.552831249999997</v>
+        <v>33.260552085</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3621,10 +1378,10 @@
         <v>6</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>35.828870835000004</v>
+        <v>33.975872914999997</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3638,10 +1395,10 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>35.036043750000005</v>
+        <v>32.736981249999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3655,10 +1412,10 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>33.397154165000003</v>
+        <v>32.757489585000002</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3672,10 +1429,10 @@
         <v>6</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E33">
-        <v>33.260552085</v>
+        <v>33.673349999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3689,10 +1446,10 @@
         <v>6</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>33.975872914999997</v>
+        <v>33.329533335000001</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3706,10 +1463,10 @@
         <v>6</v>
       </c>
       <c r="D35">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E35">
-        <v>32.736981249999999</v>
+        <v>32.118124999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3723,10 +1480,10 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E36">
-        <v>32.757489585000002</v>
+        <v>31.873402079999998</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3740,10 +1497,10 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>33.673349999999999</v>
+        <v>33.464879164999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3757,10 +1514,10 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E38">
-        <v>33.329533335000001</v>
+        <v>31.909322914999997</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3774,10 +1531,10 @@
         <v>6</v>
       </c>
       <c r="D39">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>32.118124999999999</v>
+        <v>32.123645835000005</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3791,10 +1548,10 @@
         <v>6</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E40">
-        <v>31.873402079999998</v>
+        <v>33.558141669999998</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3808,10 +1565,10 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E41">
-        <v>33.464879164999999</v>
+        <v>32.262639579999998</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3825,10 +1582,10 @@
         <v>6</v>
       </c>
       <c r="D42">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E42">
-        <v>31.909322914999997</v>
+        <v>30.907431250000002</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3842,10 +1599,10 @@
         <v>6</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>32.123645835000005</v>
+        <v>31.199858335000002</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3859,10 +1616,10 @@
         <v>6</v>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>33.558141669999998</v>
+        <v>33.22677083</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3876,10 +1633,10 @@
         <v>6</v>
       </c>
       <c r="D45">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E45">
-        <v>32.262639579999998</v>
+        <v>33.192245649999997</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3893,10 +1650,10 @@
         <v>6</v>
       </c>
       <c r="D46">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E46">
-        <v>30.907431250000002</v>
+        <v>33.070468750000003</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3910,10 +1667,10 @@
         <v>6</v>
       </c>
       <c r="D47">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E47">
-        <v>31.199858335000002</v>
+        <v>32.841475000000003</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3927,10 +1684,10 @@
         <v>6</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E48">
-        <v>33.22677083</v>
+        <v>32.907308335000003</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3944,10 +1701,10 @@
         <v>6</v>
       </c>
       <c r="D49">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E49">
-        <v>33.192245649999997</v>
+        <v>31.423169565000002</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3961,10 +1718,10 @@
         <v>6</v>
       </c>
       <c r="D50">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E50">
-        <v>33.070468750000003</v>
+        <v>31.694582610000001</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3978,10 +1735,10 @@
         <v>6</v>
       </c>
       <c r="D51">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E51">
-        <v>32.841475000000003</v>
+        <v>33.21821739</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3995,10 +1752,10 @@
         <v>6</v>
       </c>
       <c r="D52">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E52">
-        <v>32.907308335000003</v>
+        <v>33.222672914999997</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4012,10 +1769,10 @@
         <v>6</v>
       </c>
       <c r="D53">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E53">
-        <v>31.423169565000002</v>
+        <v>33.153089585000004</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4029,10 +1786,10 @@
         <v>6</v>
       </c>
       <c r="D54">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E54">
-        <v>31.694582610000001</v>
+        <v>33.338191664999997</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4043,13 +1800,13 @@
         <v>2017</v>
       </c>
       <c r="C55">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D55">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>33.21821739</v>
+        <v>33.502552080000001</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4060,13 +1817,13 @@
         <v>2017</v>
       </c>
       <c r="C56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D56">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E56">
-        <v>33.222672914999997</v>
+        <v>32.255364580000006</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4077,13 +1834,13 @@
         <v>2017</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D57">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>33.153089585000004</v>
+        <v>32.318913039999998</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4094,13 +1851,13 @@
         <v>2017</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E58">
-        <v>33.338191664999997</v>
+        <v>32.630661764999999</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4114,10 +1871,10 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59">
-        <v>33.502552080000001</v>
+        <v>32.640279164999995</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4131,10 +1888,10 @@
         <v>7</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E60">
-        <v>32.255364580000006</v>
+        <v>32.660833330000003</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4148,10 +1905,10 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E61">
-        <v>32.318913039999998</v>
+        <v>32.693802085000002</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4165,10 +1922,10 @@
         <v>7</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E62">
-        <v>32.630661764999999</v>
+        <v>32.822933335000002</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4182,10 +1939,10 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E63">
-        <v>32.640279164999995</v>
+        <v>30.980812499999999</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4199,10 +1956,10 @@
         <v>7</v>
       </c>
       <c r="D64">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E64">
-        <v>32.660833330000003</v>
+        <v>30.704547914999999</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4216,10 +1973,10 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E65">
-        <v>32.693802085000002</v>
+        <v>31.704062499999999</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4233,10 +1990,10 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E66">
-        <v>32.822933335000002</v>
+        <v>30.985433335</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4250,10 +2007,10 @@
         <v>7</v>
       </c>
       <c r="D67">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E67">
-        <v>30.980812499999999</v>
+        <v>31.045954164999998</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4267,10 +2024,10 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E68">
-        <v>30.704547914999999</v>
+        <v>29.488454165</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4284,10 +2041,10 @@
         <v>7</v>
       </c>
       <c r="D69">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E69">
-        <v>31.704062499999999</v>
+        <v>30.165954165000002</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4301,10 +2058,10 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E70">
-        <v>30.985433335</v>
+        <v>29.1649125</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4318,10 +2075,10 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E71">
-        <v>31.045954164999998</v>
+        <v>27.621024999999999</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4335,10 +2092,10 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E72">
-        <v>29.488454165</v>
+        <v>26.620433335000001</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4352,10 +2109,10 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E73">
-        <v>30.165954165000002</v>
+        <v>27.325879999999998</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4369,10 +2126,10 @@
         <v>7</v>
       </c>
       <c r="D74">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E74">
-        <v>29.1649125</v>
+        <v>26.688108334999999</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4386,10 +2143,10 @@
         <v>7</v>
       </c>
       <c r="D75">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E75">
-        <v>27.621024999999999</v>
+        <v>26.258472914999999</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4403,10 +2160,10 @@
         <v>7</v>
       </c>
       <c r="D76">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E76">
-        <v>26.620433335000001</v>
+        <v>26.600660415</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4420,10 +2177,10 @@
         <v>7</v>
       </c>
       <c r="D77">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E77">
-        <v>27.325879999999998</v>
+        <v>25.89015625</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4437,10 +2194,10 @@
         <v>7</v>
       </c>
       <c r="D78">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E78">
-        <v>26.688108334999999</v>
+        <v>25.30828125</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4454,10 +2211,10 @@
         <v>7</v>
       </c>
       <c r="D79">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E79">
-        <v>26.258472914999999</v>
+        <v>25.138679170000003</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4471,10 +2228,10 @@
         <v>7</v>
       </c>
       <c r="D80">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E80">
-        <v>26.600660415</v>
+        <v>25.019027080000001</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4488,10 +2245,10 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E81">
-        <v>25.89015625</v>
+        <v>24.744089580000001</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4505,10 +2262,10 @@
         <v>7</v>
       </c>
       <c r="D82">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E82">
-        <v>25.30828125</v>
+        <v>24.411060419999998</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4522,10 +2279,10 @@
         <v>7</v>
       </c>
       <c r="D83">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E83">
-        <v>25.138679170000003</v>
+        <v>24.093072915</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4539,10 +2296,10 @@
         <v>7</v>
       </c>
       <c r="D84">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E84">
-        <v>25.019027080000001</v>
+        <v>23.810208334999999</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4556,10 +2313,10 @@
         <v>7</v>
       </c>
       <c r="D85">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E85">
-        <v>24.744089580000001</v>
+        <v>23.598177085000003</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4570,13 +2327,13 @@
         <v>2017</v>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E86">
-        <v>24.411060419999998</v>
+        <v>23.42921875</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4587,13 +2344,13 @@
         <v>2017</v>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D87">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>24.093072915</v>
+        <v>23.28538125</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4604,13 +2361,13 @@
         <v>2017</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D88">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E88">
-        <v>23.810208334999999</v>
+        <v>23.179410415</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4621,13 +2378,13 @@
         <v>2017</v>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D89">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E89">
-        <v>23.598177085000003</v>
+        <v>23.098870830000003</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4641,10 +2398,10 @@
         <v>8</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E90">
-        <v>23.42921875</v>
+        <v>23.049047914999999</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4658,10 +2415,10 @@
         <v>8</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E91">
-        <v>23.28538125</v>
+        <v>23.02071042</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4675,78 +2432,78 @@
         <v>8</v>
       </c>
       <c r="D92">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E92">
-        <v>23.179410415</v>
+        <v>23.000104165</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A93">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B93">
         <v>2017</v>
       </c>
       <c r="C93">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D93">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E93">
-        <v>23.098870830000003</v>
+        <v>39.67890208</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A94">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B94">
         <v>2017</v>
       </c>
       <c r="C94">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E94">
-        <v>23.049047914999999</v>
+        <v>37.685016669999996</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A95">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B95">
         <v>2017</v>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E95">
-        <v>23.02071042</v>
+        <v>37.246702084999995</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A96">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B96">
         <v>2017</v>
       </c>
       <c r="C96">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E96">
-        <v>23.000104165</v>
+        <v>36.993227079999997</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4760,10 +2517,10 @@
         <v>5</v>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E97">
-        <v>35.661485714999998</v>
+        <v>36.821893750000001</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4777,10 +2534,10 @@
         <v>5</v>
       </c>
       <c r="D98">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E98">
-        <v>35.740293749999999</v>
+        <v>36.748135415</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4794,10 +2551,10 @@
         <v>5</v>
       </c>
       <c r="D99">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E99">
-        <v>35.678785415</v>
+        <v>36.724583335000005</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4811,10 +2568,10 @@
         <v>5</v>
       </c>
       <c r="D100">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E100">
-        <v>36.316597915000003</v>
+        <v>36.673602944999999</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4828,10 +2585,10 @@
         <v>5</v>
       </c>
       <c r="D101">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E101">
-        <v>39.67890208</v>
+        <v>36.618461539999998</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4845,10 +2602,10 @@
         <v>5</v>
       </c>
       <c r="D102">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E102">
-        <v>37.685016669999996</v>
+        <v>36.514375000000001</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4862,10 +2619,10 @@
         <v>5</v>
       </c>
       <c r="D103">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E103">
-        <v>37.246702084999995</v>
+        <v>37.117368749999997</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4879,10 +2636,10 @@
         <v>5</v>
       </c>
       <c r="D104">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E104">
-        <v>36.993227079999997</v>
+        <v>37.322516664999995</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4896,10 +2653,10 @@
         <v>5</v>
       </c>
       <c r="D105">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E105">
-        <v>36.821893750000001</v>
+        <v>37.45439167</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4913,10 +2670,10 @@
         <v>5</v>
       </c>
       <c r="D106">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E106">
-        <v>36.748135415</v>
+        <v>37.426789580000005</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4930,10 +2687,10 @@
         <v>5</v>
       </c>
       <c r="D107">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E107">
-        <v>36.724583335000005</v>
+        <v>37.047777080000003</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4947,10 +2704,10 @@
         <v>5</v>
       </c>
       <c r="D108">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E108">
-        <v>36.673602944999999</v>
+        <v>36.825666665</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4964,10 +2721,10 @@
         <v>5</v>
       </c>
       <c r="D109">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E109">
-        <v>36.618461539999998</v>
+        <v>36.661041664999999</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4981,10 +2738,10 @@
         <v>5</v>
       </c>
       <c r="D110">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E110">
-        <v>36.514375000000001</v>
+        <v>36.674183330000005</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -4998,10 +2755,10 @@
         <v>5</v>
       </c>
       <c r="D111">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E111">
-        <v>37.117368749999997</v>
+        <v>36.477674999999998</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5015,10 +2772,10 @@
         <v>5</v>
       </c>
       <c r="D112">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E112">
-        <v>37.322516664999995</v>
+        <v>36.358166664999999</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5032,10 +2789,10 @@
         <v>5</v>
       </c>
       <c r="D113">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E113">
-        <v>37.45439167</v>
+        <v>36.734479164999996</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5049,10 +2806,10 @@
         <v>5</v>
       </c>
       <c r="D114">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E114">
-        <v>37.426789580000005</v>
+        <v>37.082826085000001</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5066,10 +2823,10 @@
         <v>5</v>
       </c>
       <c r="D115">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E115">
-        <v>37.047777080000003</v>
+        <v>36.564860420000002</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5080,13 +2837,13 @@
         <v>2017</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D116">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E116">
-        <v>36.825666665</v>
+        <v>37.147760419999997</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5097,13 +2854,13 @@
         <v>2017</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D117">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E117">
-        <v>36.661041664999999</v>
+        <v>37.484391665000004</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5114,13 +2871,13 @@
         <v>2017</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D118">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E118">
-        <v>36.674183330000005</v>
+        <v>36.79265625</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5131,13 +2888,13 @@
         <v>2017</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D119">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E119">
-        <v>36.477674999999998</v>
+        <v>35.5720125</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5148,13 +2905,13 @@
         <v>2017</v>
       </c>
       <c r="C120">
+        <v>6</v>
+      </c>
+      <c r="D120">
         <v>5</v>
       </c>
-      <c r="D120">
-        <v>28</v>
-      </c>
       <c r="E120">
-        <v>36.358166664999999</v>
+        <v>36.903171740000005</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5165,13 +2922,13 @@
         <v>2017</v>
       </c>
       <c r="C121">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D121">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E121">
-        <v>36.734479164999996</v>
+        <v>37.368820835000001</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5182,13 +2939,13 @@
         <v>2017</v>
       </c>
       <c r="C122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D122">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E122">
-        <v>37.082826085000001</v>
+        <v>35.979708329999994</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5199,13 +2956,13 @@
         <v>2017</v>
       </c>
       <c r="C123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D123">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E123">
-        <v>36.564860420000002</v>
+        <v>36.202241665000003</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5219,10 +2976,10 @@
         <v>6</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E124">
-        <v>37.147760419999997</v>
+        <v>37.053110414999999</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5236,10 +2993,10 @@
         <v>6</v>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E125">
-        <v>37.484391665000004</v>
+        <v>36.489322915000002</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5253,10 +3010,10 @@
         <v>6</v>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E126">
-        <v>36.79265625</v>
+        <v>34.814860414999998</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5270,10 +3027,10 @@
         <v>6</v>
       </c>
       <c r="D127">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E127">
-        <v>35.5720125</v>
+        <v>35.155345835000006</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5287,10 +3044,10 @@
         <v>6</v>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E128">
-        <v>36.903171740000005</v>
+        <v>38.165625000000006</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5304,10 +3061,10 @@
         <v>6</v>
       </c>
       <c r="D129">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E129">
-        <v>37.368820835000001</v>
+        <v>36.392793749999996</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5321,10 +3078,10 @@
         <v>6</v>
       </c>
       <c r="D130">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E130">
-        <v>35.979708329999994</v>
+        <v>36.449929170000004</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5338,10 +3095,10 @@
         <v>6</v>
       </c>
       <c r="D131">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E131">
-        <v>36.202241665000003</v>
+        <v>38.504495835</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5355,10 +3112,10 @@
         <v>6</v>
       </c>
       <c r="D132">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E132">
-        <v>37.053110414999999</v>
+        <v>37.675520829999996</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5372,10 +3129,10 @@
         <v>6</v>
       </c>
       <c r="D133">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E133">
-        <v>36.489322915000002</v>
+        <v>35.865625000000001</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5389,10 +3146,10 @@
         <v>6</v>
       </c>
       <c r="D134">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E134">
-        <v>34.814860414999998</v>
+        <v>35.602031249999996</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5406,10 +3163,10 @@
         <v>6</v>
       </c>
       <c r="D135">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E135">
-        <v>35.155345835000006</v>
+        <v>37.106493749999998</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5423,10 +3180,10 @@
         <v>6</v>
       </c>
       <c r="D136">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E136">
-        <v>38.165625000000006</v>
+        <v>38.405523909999999</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5440,10 +3197,10 @@
         <v>6</v>
       </c>
       <c r="D137">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E137">
-        <v>36.392793749999996</v>
+        <v>38.067656249999999</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5457,10 +3214,10 @@
         <v>6</v>
       </c>
       <c r="D138">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E138">
-        <v>36.449929170000004</v>
+        <v>38.097135414999997</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5474,10 +3231,10 @@
         <v>6</v>
       </c>
       <c r="D139">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E139">
-        <v>38.504495835</v>
+        <v>37.843612499999999</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5491,10 +3248,10 @@
         <v>6</v>
       </c>
       <c r="D140">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E140">
-        <v>37.675520829999996</v>
+        <v>35.665978260000003</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5508,10 +3265,10 @@
         <v>6</v>
       </c>
       <c r="D141">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E141">
-        <v>35.865625000000001</v>
+        <v>35.101717395000001</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5525,10 +3282,10 @@
         <v>6</v>
       </c>
       <c r="D142">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E142">
-        <v>35.602031249999996</v>
+        <v>36.000091304999998</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5542,10 +3299,10 @@
         <v>6</v>
       </c>
       <c r="D143">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E143">
-        <v>37.106493749999998</v>
+        <v>36.723297915000003</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5559,10 +3316,10 @@
         <v>6</v>
       </c>
       <c r="D144">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E144">
-        <v>38.405523909999999</v>
+        <v>35.931145834999995</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5576,10 +3333,10 @@
         <v>6</v>
       </c>
       <c r="D145">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E145">
-        <v>38.067656249999999</v>
+        <v>36.550535414999999</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5590,13 +3347,13 @@
         <v>2017</v>
       </c>
       <c r="C146">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D146">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E146">
-        <v>38.097135414999997</v>
+        <v>36.878462499999998</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5607,13 +3364,13 @@
         <v>2017</v>
       </c>
       <c r="C147">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D147">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E147">
-        <v>37.843612499999999</v>
+        <v>35.234252085000001</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5624,13 +3381,13 @@
         <v>2017</v>
       </c>
       <c r="C148">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D148">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E148">
-        <v>35.665978260000003</v>
+        <v>36.337952170000001</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5641,13 +3398,13 @@
         <v>2017</v>
       </c>
       <c r="C149">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D149">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E149">
-        <v>35.101717395000001</v>
+        <v>36.452329415000001</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5658,13 +3415,13 @@
         <v>2017</v>
       </c>
       <c r="C150">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D150">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E150">
-        <v>36.000091304999998</v>
+        <v>37.194512500000002</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5675,13 +3432,13 @@
         <v>2017</v>
       </c>
       <c r="C151">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D151">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E151">
-        <v>36.723297915000003</v>
+        <v>37.015764584999999</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5692,13 +3449,13 @@
         <v>2017</v>
       </c>
       <c r="C152">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D152">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E152">
-        <v>35.931145834999995</v>
+        <v>37.150693750000002</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5709,13 +3466,13 @@
         <v>2017</v>
       </c>
       <c r="C153">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D153">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E153">
-        <v>36.550535414999999</v>
+        <v>36.580279165</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5729,10 +3486,10 @@
         <v>7</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E154">
-        <v>36.878462499999998</v>
+        <v>34.399304165000004</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5746,10 +3503,10 @@
         <v>7</v>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E155">
-        <v>35.234252085000001</v>
+        <v>35.5215125</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5763,10 +3520,10 @@
         <v>7</v>
       </c>
       <c r="D156">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E156">
-        <v>36.337952170000001</v>
+        <v>37.076214585000002</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5780,10 +3537,10 @@
         <v>7</v>
       </c>
       <c r="D157">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E157">
-        <v>36.452329415000001</v>
+        <v>37.761372914999995</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5797,10 +3554,10 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E158">
-        <v>37.194512500000002</v>
+        <v>37.664739580000003</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5814,10 +3571,10 @@
         <v>7</v>
       </c>
       <c r="D159">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E159">
-        <v>37.015764584999999</v>
+        <v>38.682795835</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5831,10 +3588,10 @@
         <v>7</v>
       </c>
       <c r="D160">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E160">
-        <v>37.150693750000002</v>
+        <v>38.140593750000001</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5848,10 +3605,10 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E161">
-        <v>36.580279165</v>
+        <v>36.503333330000004</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5865,10 +3622,10 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E162">
-        <v>34.399304165000004</v>
+        <v>35.173558334999996</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5882,10 +3639,10 @@
         <v>7</v>
       </c>
       <c r="D163">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E163">
-        <v>35.5215125</v>
+        <v>37.059739585000003</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5899,10 +3656,10 @@
         <v>7</v>
       </c>
       <c r="D164">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E164">
-        <v>37.076214585000002</v>
+        <v>38.397374999999997</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5916,10 +3673,10 @@
         <v>7</v>
       </c>
       <c r="D165">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E165">
-        <v>37.761372914999995</v>
+        <v>36.938506250000003</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5933,10 +3690,10 @@
         <v>7</v>
       </c>
       <c r="D166">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E166">
-        <v>37.664739580000003</v>
+        <v>37.489177085000001</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5950,10 +3707,10 @@
         <v>7</v>
       </c>
       <c r="D167">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E167">
-        <v>38.682795835</v>
+        <v>38.456389584999997</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5967,10 +3724,10 @@
         <v>7</v>
       </c>
       <c r="D168">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E168">
-        <v>38.140593750000001</v>
+        <v>37.091652080000003</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -5984,10 +3741,10 @@
         <v>7</v>
       </c>
       <c r="D169">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E169">
-        <v>36.503333330000004</v>
+        <v>37.197987499999996</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6001,10 +3758,10 @@
         <v>7</v>
       </c>
       <c r="D170">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E170">
-        <v>35.173558334999996</v>
+        <v>38.318837500000001</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6018,10 +3775,10 @@
         <v>7</v>
       </c>
       <c r="D171">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E171">
-        <v>37.059739585000003</v>
+        <v>37.428318750000003</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6035,10 +3792,10 @@
         <v>7</v>
       </c>
       <c r="D172">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E172">
-        <v>38.397374999999997</v>
+        <v>36.472172915000002</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6052,10 +3809,10 @@
         <v>7</v>
       </c>
       <c r="D173">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E173">
-        <v>36.938506250000003</v>
+        <v>35.359270835000004</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6069,10 +3826,10 @@
         <v>7</v>
       </c>
       <c r="D174">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E174">
-        <v>37.489177085000001</v>
+        <v>33.79243125</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6086,10 +3843,10 @@
         <v>7</v>
       </c>
       <c r="D175">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E175">
-        <v>38.456389584999997</v>
+        <v>31.9542875</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6103,10 +3860,10 @@
         <v>7</v>
       </c>
       <c r="D176">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E176">
-        <v>37.091652080000003</v>
+        <v>30.140641670000001</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6117,13 +3874,13 @@
         <v>2017</v>
       </c>
       <c r="C177">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D177">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E177">
-        <v>37.197987499999996</v>
+        <v>28.4892</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6134,13 +3891,13 @@
         <v>2017</v>
       </c>
       <c r="C178">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D178">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E178">
-        <v>38.318837500000001</v>
+        <v>27.4386625</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6151,13 +3908,13 @@
         <v>2017</v>
       </c>
       <c r="C179">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D179">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E179">
-        <v>37.428318750000003</v>
+        <v>27.26095625</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6168,13 +3925,13 @@
         <v>2017</v>
       </c>
       <c r="C180">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D180">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E180">
-        <v>36.472172915000002</v>
+        <v>27.132764585</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6185,13 +3942,13 @@
         <v>2017</v>
       </c>
       <c r="C181">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D181">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E181">
-        <v>35.359270835000004</v>
+        <v>26.865450000000003</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6202,13 +3959,13 @@
         <v>2017</v>
       </c>
       <c r="C182">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D182">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E182">
-        <v>33.79243125</v>
+        <v>26.632708335</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6219,149 +3976,149 @@
         <v>2017</v>
       </c>
       <c r="C183">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D183">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E183">
-        <v>31.9542875</v>
+        <v>26.318662500000002</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A184">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B184">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C184">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D184">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E184">
-        <v>30.140641670000001</v>
+        <v>43.51267</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A185">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B185">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C185">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E185">
-        <v>28.4892</v>
+        <v>42.44678571</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A186">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B186">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C186">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D186">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E186">
-        <v>27.4386625</v>
+        <v>42.061668179999998</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A187">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B187">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C187">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E187">
-        <v>27.26095625</v>
+        <v>43.051949999999998</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A188">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B188">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C188">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D188">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188">
-        <v>27.132764585</v>
+        <v>42.944312500000002</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A189">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B189">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C189">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E189">
-        <v>26.865450000000003</v>
+        <v>42.098042499999998</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A190">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B190">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C190">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D190">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E190">
-        <v>26.632708335</v>
+        <v>41.074832499999999</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A191">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B191">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C191">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D191">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E191">
-        <v>26.318662500000002</v>
+        <v>42.163145450000002</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6372,13 +4129,13 @@
         <v>2018</v>
       </c>
       <c r="C192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D192">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E192">
-        <v>38.50486111</v>
+        <v>42.523405259999997</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6389,13 +4146,13 @@
         <v>2018</v>
       </c>
       <c r="C193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D193">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E193">
-        <v>38.818835419999999</v>
+        <v>41.309708819999997</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6406,13 +4163,13 @@
         <v>2018</v>
       </c>
       <c r="C194">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D194">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E194">
-        <v>39.44848958</v>
+        <v>42.363900000000001</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6423,13 +4180,13 @@
         <v>2018</v>
       </c>
       <c r="C195">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D195">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E195">
-        <v>39.353785420000001</v>
+        <v>42.374747370000001</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6440,13 +4197,13 @@
         <v>2018</v>
       </c>
       <c r="C196">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D196">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E196">
-        <v>39.036958329999997</v>
+        <v>41.289527499999998</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6457,13 +4214,13 @@
         <v>2018</v>
       </c>
       <c r="C197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D197">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E197">
-        <v>38.477743750000002</v>
+        <v>40.452647059999997</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6474,13 +4231,13 @@
         <v>2018</v>
       </c>
       <c r="C198">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D198">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E198">
-        <v>38.459166670000002</v>
+        <v>39.440093179999998</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6491,13 +4248,13 @@
         <v>2018</v>
       </c>
       <c r="C199">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D199">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E199">
-        <v>38.786354170000003</v>
+        <v>38.287047919999999</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6508,13 +4265,13 @@
         <v>2018</v>
       </c>
       <c r="C200">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D200">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E200">
-        <v>38.897760419999997</v>
+        <v>40.241370830000001</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6525,13 +4282,13 @@
         <v>2018</v>
       </c>
       <c r="C201">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D201">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E201">
-        <v>38.85430625</v>
+        <v>42.390875000000001</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6542,13 +4299,13 @@
         <v>2018</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D202">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E202">
-        <v>38.988595830000001</v>
+        <v>40.893233330000001</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6559,13 +4316,13 @@
         <v>2018</v>
       </c>
       <c r="C203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D203">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E203">
-        <v>39.020106249999998</v>
+        <v>40.177185420000001</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6576,13 +4333,13 @@
         <v>2018</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D204">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E204">
-        <v>39.254056669999997</v>
+        <v>39.774360420000001</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6593,13 +4350,13 @@
         <v>2018</v>
       </c>
       <c r="C205">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D205">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E205">
-        <v>39.976428570000003</v>
+        <v>39.32453125</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6610,13 +4367,13 @@
         <v>2018</v>
       </c>
       <c r="C206">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D206">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E206">
-        <v>39.957935419999998</v>
+        <v>40.977849999999997</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6627,13 +4384,13 @@
         <v>2018</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D207">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E207">
-        <v>40.11982708</v>
+        <v>41.562047919999998</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6644,13 +4401,13 @@
         <v>2018</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D208">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E208">
-        <v>40.564877080000002</v>
+        <v>40.709635419999998</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6661,13 +4418,13 @@
         <v>2018</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D209">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E209">
-        <v>40.762519050000002</v>
+        <v>40.6347375</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6678,13 +4435,13 @@
         <v>2018</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D210">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E210">
-        <v>43.51267</v>
+        <v>39.867258329999999</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6695,13 +4452,13 @@
         <v>2018</v>
       </c>
       <c r="C211">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D211">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E211">
-        <v>42.44678571</v>
+        <v>39.152308329999997</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6712,13 +4469,13 @@
         <v>2018</v>
       </c>
       <c r="C212">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D212">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E212">
-        <v>42.061668179999998</v>
+        <v>40.21368125</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6732,10 +4489,10 @@
         <v>6</v>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E213">
-        <v>43.051949999999998</v>
+        <v>41.11743542</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6749,10 +4506,10 @@
         <v>6</v>
       </c>
       <c r="D214">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E214">
-        <v>42.944312500000002</v>
+        <v>41.85220417</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6766,10 +4523,10 @@
         <v>6</v>
       </c>
       <c r="D215">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E215">
-        <v>42.098042499999998</v>
+        <v>41.557135420000002</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6783,10 +4540,10 @@
         <v>6</v>
       </c>
       <c r="D216">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E216">
-        <v>41.074832499999999</v>
+        <v>40.712150000000001</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6797,13 +4554,13 @@
         <v>2018</v>
       </c>
       <c r="C217">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D217">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E217">
-        <v>42.163145450000002</v>
+        <v>40.261304170000003</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6814,13 +4571,13 @@
         <v>2018</v>
       </c>
       <c r="C218">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D218">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E218">
-        <v>42.523405259999997</v>
+        <v>42.044116670000001</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6831,13 +4588,13 @@
         <v>2018</v>
       </c>
       <c r="C219">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D219">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E219">
-        <v>41.309708819999997</v>
+        <v>42.699545829999998</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6848,13 +4605,13 @@
         <v>2018</v>
       </c>
       <c r="C220">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D220">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E220">
-        <v>42.363900000000001</v>
+        <v>43.446245830000002</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6865,13 +4622,13 @@
         <v>2018</v>
       </c>
       <c r="C221">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D221">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E221">
-        <v>42.374747370000001</v>
+        <v>43.049799999999998</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6882,13 +4639,13 @@
         <v>2018</v>
       </c>
       <c r="C222">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D222">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E222">
-        <v>41.289527499999998</v>
+        <v>43.39211667</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6899,13 +4656,13 @@
         <v>2018</v>
       </c>
       <c r="C223">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D223">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E223">
-        <v>40.452647059999997</v>
+        <v>43.11012083</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6916,13 +4673,13 @@
         <v>2018</v>
       </c>
       <c r="C224">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D224">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E224">
-        <v>39.440093179999998</v>
+        <v>41.735439579999998</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6933,13 +4690,13 @@
         <v>2018</v>
       </c>
       <c r="C225">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D225">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E225">
-        <v>38.287047919999999</v>
+        <v>42.299947920000001</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6950,13 +4707,13 @@
         <v>2018</v>
       </c>
       <c r="C226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D226">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E226">
-        <v>40.241370830000001</v>
+        <v>42.471195829999999</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6967,13 +4724,13 @@
         <v>2018</v>
       </c>
       <c r="C227">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D227">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E227">
-        <v>42.390875000000001</v>
+        <v>42.804099999999998</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -6984,13 +4741,13 @@
         <v>2018</v>
       </c>
       <c r="C228">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D228">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E228">
-        <v>40.893233330000001</v>
+        <v>42.653125000000003</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7001,13 +4758,13 @@
         <v>2018</v>
       </c>
       <c r="C229">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D229">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E229">
-        <v>40.177185420000001</v>
+        <v>43.447256250000002</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7018,13 +4775,13 @@
         <v>2018</v>
       </c>
       <c r="C230">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D230">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E230">
-        <v>39.774360420000001</v>
+        <v>43.08128542</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7035,13 +4792,13 @@
         <v>2018</v>
       </c>
       <c r="C231">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D231">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E231">
-        <v>39.32453125</v>
+        <v>42.131720829999999</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7052,13 +4809,13 @@
         <v>2018</v>
       </c>
       <c r="C232">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D232">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E232">
-        <v>40.977849999999997</v>
+        <v>41.4729375</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7069,13 +4826,13 @@
         <v>2018</v>
       </c>
       <c r="C233">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D233">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E233">
-        <v>41.562047919999998</v>
+        <v>41.00368125</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7086,13 +4843,13 @@
         <v>2018</v>
       </c>
       <c r="C234">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D234">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E234">
-        <v>40.709635419999998</v>
+        <v>41.661564579999997</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7103,13 +4860,13 @@
         <v>2018</v>
       </c>
       <c r="C235">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D235">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E235">
-        <v>40.6347375</v>
+        <v>41.894539469999998</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7120,13 +4877,13 @@
         <v>2018</v>
       </c>
       <c r="C236">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D236">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E236">
-        <v>39.867258329999999</v>
+        <v>42.49291667</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7137,13 +4894,13 @@
         <v>2018</v>
       </c>
       <c r="C237">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D237">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E237">
-        <v>39.152308329999997</v>
+        <v>42.72170208</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7154,13 +4911,13 @@
         <v>2018</v>
       </c>
       <c r="C238">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D238">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E238">
-        <v>40.21368125</v>
+        <v>41.770625000000003</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7171,13 +4928,13 @@
         <v>2018</v>
       </c>
       <c r="C239">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D239">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E239">
-        <v>41.11743542</v>
+        <v>42.263627079999999</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7188,13 +4945,13 @@
         <v>2018</v>
       </c>
       <c r="C240">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D240">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E240">
-        <v>41.85220417</v>
+        <v>42.627047920000003</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7205,13 +4962,13 @@
         <v>2018</v>
       </c>
       <c r="C241">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D241">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E241">
-        <v>41.557135420000002</v>
+        <v>41.705089579999999</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7222,13 +4979,13 @@
         <v>2018</v>
       </c>
       <c r="C242">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D242">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E242">
-        <v>40.712150000000001</v>
+        <v>40.992258329999999</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7242,10 +4999,10 @@
         <v>7</v>
       </c>
       <c r="D243">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E243">
-        <v>40.261304170000003</v>
+        <v>40.239212500000001</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7259,10 +5016,10 @@
         <v>7</v>
       </c>
       <c r="D244">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E244">
-        <v>42.044116670000001</v>
+        <v>39.422239580000003</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7276,10 +5033,10 @@
         <v>7</v>
       </c>
       <c r="D245">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E245">
-        <v>42.699545829999998</v>
+        <v>38.547033329999998</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7293,10 +5050,10 @@
         <v>7</v>
       </c>
       <c r="D246">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E246">
-        <v>43.446245830000002</v>
+        <v>37.558889579999999</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7310,10 +5067,10 @@
         <v>7</v>
       </c>
       <c r="D247">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="E247">
-        <v>43.049799999999998</v>
+        <v>36.151291669999999</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7324,13 +5081,13 @@
         <v>2018</v>
       </c>
       <c r="C248">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D248">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E248">
-        <v>43.39211667</v>
+        <v>34.342708330000001</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7341,13 +5098,13 @@
         <v>2018</v>
       </c>
       <c r="C249">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D249">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E249">
-        <v>43.11012083</v>
+        <v>32.055622919999998</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7358,13 +5115,13 @@
         <v>2018</v>
       </c>
       <c r="C250">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D250">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E250">
-        <v>41.735439579999998</v>
+        <v>30.649643749999999</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7375,13 +5132,13 @@
         <v>2018</v>
       </c>
       <c r="C251">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D251">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E251">
-        <v>42.299947920000001</v>
+        <v>30.015379169999999</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7392,455 +5149,455 @@
         <v>2018</v>
       </c>
       <c r="C252">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D252">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E252">
-        <v>42.471195829999999</v>
+        <v>29.389184090000001</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A253">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B253">
         <v>2018</v>
       </c>
       <c r="C253">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D253">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E253">
-        <v>42.804099999999998</v>
+        <v>44.136884999999999</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A254">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B254">
         <v>2018</v>
       </c>
       <c r="C254">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D254">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E254">
-        <v>42.653125000000003</v>
+        <v>43.441457499999991</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A255">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B255">
         <v>2018</v>
       </c>
       <c r="C255">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D255">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E255">
-        <v>43.447256250000002</v>
+        <v>41.309562499999991</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A256">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B256">
         <v>2018</v>
       </c>
       <c r="C256">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D256">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E256">
-        <v>43.08128542</v>
+        <v>40.59755454545455</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A257">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B257">
         <v>2018</v>
       </c>
       <c r="C257">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D257">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E257">
-        <v>42.131720829999999</v>
+        <v>41.987449999999995</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A258">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B258">
         <v>2018</v>
       </c>
       <c r="C258">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D258">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E258">
-        <v>41.4729375</v>
+        <v>39.344897058823534</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A259">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B259">
         <v>2018</v>
       </c>
       <c r="C259">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D259">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E259">
-        <v>41.00368125</v>
+        <v>41.283935</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A260">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B260">
         <v>2018</v>
       </c>
       <c r="C260">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D260">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E260">
-        <v>41.661564579999997</v>
+        <v>45.289013157894722</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A261">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B261">
         <v>2018</v>
       </c>
       <c r="C261">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D261">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E261">
-        <v>41.894539469999998</v>
+        <v>44.087687500000001</v>
       </c>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A262">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B262">
         <v>2018</v>
       </c>
       <c r="C262">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D262">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E262">
-        <v>42.49291667</v>
+        <v>42.967155882352948</v>
       </c>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A263">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B263">
         <v>2018</v>
       </c>
       <c r="C263">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D263">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E263">
-        <v>42.72170208</v>
+        <v>40.781477272727265</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A264">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B264">
         <v>2018</v>
       </c>
       <c r="C264">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D264">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E264">
-        <v>41.770625000000003</v>
+        <v>38.044947916666679</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A265">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B265">
         <v>2018</v>
       </c>
       <c r="C265">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D265">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E265">
-        <v>42.263627079999999</v>
+        <v>39.930695833333338</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A266">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B266">
         <v>2018</v>
       </c>
       <c r="C266">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D266">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E266">
-        <v>42.627047920000003</v>
+        <v>43.071042500000004</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A267">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B267">
         <v>2018</v>
       </c>
       <c r="C267">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D267">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E267">
-        <v>41.705089579999999</v>
+        <v>41.284220833333336</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A268">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B268">
         <v>2018</v>
       </c>
       <c r="C268">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D268">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E268">
-        <v>40.992258329999999</v>
+        <v>40.396162499999996</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A269">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B269">
         <v>2018</v>
       </c>
       <c r="C269">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D269">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E269">
-        <v>40.239212500000001</v>
+        <v>39.649014583333326</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A270">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B270">
         <v>2018</v>
       </c>
       <c r="C270">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D270">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E270">
-        <v>39.422239580000003</v>
+        <v>38.624235416666671</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A271">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B271">
         <v>2018</v>
       </c>
       <c r="C271">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D271">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E271">
-        <v>38.547033329999998</v>
+        <v>40.130850000000002</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A272">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B272">
         <v>2018</v>
       </c>
       <c r="C272">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D272">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E272">
-        <v>37.558889579999999</v>
+        <v>40.892031249999995</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A273">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B273">
         <v>2018</v>
       </c>
       <c r="C273">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D273">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E273">
-        <v>36.151291669999999</v>
+        <v>39.834895833333327</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A274">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B274">
         <v>2018</v>
       </c>
       <c r="C274">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E274">
-        <v>34.342708330000001</v>
+        <v>39.614008333333338</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A275">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B275">
         <v>2018</v>
       </c>
       <c r="C275">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D275">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E275">
-        <v>32.055622919999998</v>
+        <v>38.565970833333331</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A276">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B276">
         <v>2018</v>
       </c>
       <c r="C276">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D276">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E276">
-        <v>30.649643749999999</v>
+        <v>37.45817916666666</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A277">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B277">
         <v>2018</v>
       </c>
       <c r="C277">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D277">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E277">
-        <v>30.015379169999999</v>
+        <v>38.100518750000006</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A278">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B278">
         <v>2018</v>
       </c>
       <c r="C278">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D278">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E278">
-        <v>29.389184090000001</v>
+        <v>38.857658333333326</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7851,13 +5608,13 @@
         <v>2018</v>
       </c>
       <c r="C279">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D279">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E279">
-        <v>40.650927777777774</v>
+        <v>40.107954166666666</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7868,13 +5625,13 @@
         <v>2018</v>
       </c>
       <c r="C280">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D280">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E280">
-        <v>41.047499999999985</v>
+        <v>40.295762500000002</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7885,13 +5642,13 @@
         <v>2018</v>
       </c>
       <c r="C281">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D281">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E281">
-        <v>41.69001875</v>
+        <v>38.987212500000005</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7902,13 +5659,13 @@
         <v>2018</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D282">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E282">
-        <v>41.609931249999995</v>
+        <v>38.121416666666654</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7919,13 +5676,13 @@
         <v>2018</v>
       </c>
       <c r="C283">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D283">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E283">
-        <v>41.40442083333334</v>
+        <v>40.494114583333342</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7936,13 +5693,13 @@
         <v>2018</v>
       </c>
       <c r="C284">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D284">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E284">
-        <v>40.656162500000001</v>
+        <v>41.521456250000007</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7953,13 +5710,13 @@
         <v>2018</v>
       </c>
       <c r="C285">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D285">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E285">
-        <v>40.577152083333331</v>
+        <v>41.320939583333335</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7970,13 +5727,13 @@
         <v>2018</v>
       </c>
       <c r="C286">
+        <v>7</v>
+      </c>
+      <c r="D286">
         <v>5</v>
       </c>
-      <c r="D286">
-        <v>18</v>
-      </c>
       <c r="E286">
-        <v>40.905935416666672</v>
+        <v>40.903390909090916</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -7987,13 +5744,13 @@
         <v>2018</v>
       </c>
       <c r="C287">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D287">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E287">
-        <v>41.059912500000003</v>
+        <v>41.556806249999994</v>
       </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8004,13 +5761,13 @@
         <v>2018</v>
       </c>
       <c r="C288">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D288">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E288">
-        <v>41.17557291666666</v>
+        <v>41.487068749999985</v>
       </c>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8021,13 +5778,13 @@
         <v>2018</v>
       </c>
       <c r="C289">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D289">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E289">
-        <v>41.375222916666665</v>
+        <v>40.106562499999995</v>
       </c>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8038,13 +5795,13 @@
         <v>2018</v>
       </c>
       <c r="C290">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D290">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E290">
-        <v>41.464966666666669</v>
+        <v>40.912622916666663</v>
       </c>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8055,13 +5812,13 @@
         <v>2018</v>
       </c>
       <c r="C291">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D291">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E291">
-        <v>41.778416666666665</v>
+        <v>41.050587499999999</v>
       </c>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8072,13 +5829,13 @@
         <v>2018</v>
       </c>
       <c r="C292">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D292">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E292">
-        <v>42.770364285714287</v>
+        <v>41.461433333333332</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8089,13 +5846,13 @@
         <v>2018</v>
       </c>
       <c r="C293">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D293">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E293">
-        <v>42.708595833333334</v>
+        <v>41.316927083333333</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8106,13 +5863,13 @@
         <v>2018</v>
       </c>
       <c r="C294">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D294">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E294">
-        <v>42.831929166666662</v>
+        <v>42.214706249999999</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8123,13 +5880,13 @@
         <v>2018</v>
       </c>
       <c r="C295">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D295">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E295">
-        <v>42.881181250000004</v>
+        <v>41.724706250000004</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8140,13 +5897,13 @@
         <v>2018</v>
       </c>
       <c r="C296">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D296">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E296">
-        <v>42.724082499999994</v>
+        <v>40.550508333333326</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8157,13 +5914,13 @@
         <v>2018</v>
       </c>
       <c r="C297">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D297">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E297">
-        <v>43.692991666666671</v>
+        <v>39.657872499999996</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8174,13 +5931,13 @@
         <v>2018</v>
       </c>
       <c r="C298">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D298">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E298">
-        <v>43.788199999999996</v>
+        <v>39.038333333333334</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8191,13 +5948,13 @@
         <v>2018</v>
       </c>
       <c r="C299">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D299">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E299">
-        <v>43.690202380952378</v>
+        <v>39.737516666666664</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8208,13 +5965,13 @@
         <v>2018</v>
       </c>
       <c r="C300">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D300">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E300">
-        <v>43.930244736842099</v>
+        <v>39.826684210526317</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8225,13 +5982,13 @@
         <v>2018</v>
       </c>
       <c r="C301">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D301">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E301">
-        <v>44.136884999999999</v>
+        <v>41.034704166666664</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8242,13 +5999,13 @@
         <v>2018</v>
       </c>
       <c r="C302">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D302">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E302">
-        <v>43.441457499999991</v>
+        <v>41.426093750000007</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8259,13 +6016,13 @@
         <v>2018</v>
       </c>
       <c r="C303">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D303">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E303">
-        <v>41.309562499999991</v>
+        <v>40.133804166666678</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8276,13 +6033,13 @@
         <v>2018</v>
       </c>
       <c r="C304">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D304">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E304">
-        <v>40.59755454545455</v>
+        <v>40.283127083333333</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8293,13 +6050,13 @@
         <v>2018</v>
       </c>
       <c r="C305">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D305">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E305">
-        <v>41.987449999999995</v>
+        <v>40.736441666666671</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8310,13 +6067,13 @@
         <v>2018</v>
       </c>
       <c r="C306">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D306">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E306">
-        <v>39.344897058823534</v>
+        <v>39.704927083333331</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8327,13 +6084,13 @@
         <v>2018</v>
       </c>
       <c r="C307">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D307">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E307">
-        <v>41.283935</v>
+        <v>38.572920833333335</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8344,13 +6101,13 @@
         <v>2018</v>
       </c>
       <c r="C308">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D308">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E308">
-        <v>45.289013157894722</v>
+        <v>36.853506250000002</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8361,13 +6118,13 @@
         <v>2018</v>
       </c>
       <c r="C309">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D309">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E309">
-        <v>44.087687500000001</v>
+        <v>34.042012499999991</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8378,13 +6135,13 @@
         <v>2018</v>
       </c>
       <c r="C310">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D310">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="E310">
-        <v>42.967155882352948</v>
+        <v>31.083460416666668</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8395,13 +6152,13 @@
         <v>2018</v>
       </c>
       <c r="C311">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D311">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E311">
-        <v>40.781477272727265</v>
+        <v>28.825729166666665</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8412,13 +6169,13 @@
         <v>2018</v>
       </c>
       <c r="C312">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D312">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="E312">
-        <v>38.044947916666679</v>
+        <v>27.386275000000001</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8429,13 +6186,13 @@
         <v>2018</v>
       </c>
       <c r="C313">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D313">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E313">
-        <v>39.930695833333338</v>
+        <v>26.241041666666661</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8446,13 +6203,13 @@
         <v>2018</v>
       </c>
       <c r="C314">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D314">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E314">
-        <v>43.071042500000004</v>
+        <v>25.3863375</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8463,13 +6220,13 @@
         <v>2018</v>
       </c>
       <c r="C315">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D315">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E315">
-        <v>41.284220833333336</v>
+        <v>24.923489583333335</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8480,13 +6237,13 @@
         <v>2018</v>
       </c>
       <c r="C316">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D316">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E316">
-        <v>40.396162499999996</v>
+        <v>24.503662500000001</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -8497,69 +6254,69 @@
         <v>2018</v>
       </c>
       <c r="C317">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D317">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E317">
-        <v>39.649014583333326</v>
+        <v>24.220284090909093</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A318">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B318">
         <v>2018</v>
       </c>
       <c r="C318">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D318">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E318">
-        <v>38.624235416666671</v>
+        <v>43.693214285714284</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A319">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B319">
         <v>2018</v>
       </c>
       <c r="C319">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D319">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E319">
-        <v>40.130850000000002</v>
+        <v>43.472710714285711</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A320">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B320">
         <v>2018</v>
       </c>
       <c r="C320">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D320">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E320">
-        <v>40.892031249999995</v>
+        <v>43.174980000000005</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A321">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B321">
         <v>2018</v>
@@ -8568,15 +6325,15 @@
         <v>6</v>
       </c>
       <c r="D321">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E321">
-        <v>39.834895833333327</v>
+        <v>42.811390476190475</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A322">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B322">
         <v>2018</v>
@@ -8585,15 +6342,15 @@
         <v>6</v>
       </c>
       <c r="D322">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E322">
-        <v>39.614008333333338</v>
+        <v>42.446414999999995</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A323">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B323">
         <v>2018</v>
@@ -8602,15 +6359,15 @@
         <v>6</v>
       </c>
       <c r="D323">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E323">
-        <v>38.565970833333331</v>
+        <v>41.877272500000004</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A324">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B324">
         <v>2018</v>
@@ -8619,15 +6376,15 @@
         <v>6</v>
       </c>
       <c r="D324">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E324">
-        <v>37.45817916666666</v>
+        <v>41.083562500000006</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A325">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B325">
         <v>2018</v>
@@ -8636,15 +6393,15 @@
         <v>6</v>
       </c>
       <c r="D325">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E325">
-        <v>38.100518750000006</v>
+        <v>39.908275000000003</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A326">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B326">
         <v>2018</v>
@@ -8653,15 +6410,15 @@
         <v>6</v>
       </c>
       <c r="D326">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E326">
-        <v>38.857658333333326</v>
+        <v>38.772549999999995</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A327">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B327">
         <v>2018</v>
@@ -8670,15 +6427,15 @@
         <v>6</v>
       </c>
       <c r="D327">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E327">
-        <v>40.107954166666666</v>
+        <v>37.392376470588232</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A328">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B328">
         <v>2018</v>
@@ -8687,15 +6444,15 @@
         <v>6</v>
       </c>
       <c r="D328">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E328">
-        <v>40.295762500000002</v>
+        <v>37.843442105263158</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A329">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B329">
         <v>2018</v>
@@ -8704,372 +6461,372 @@
         <v>6</v>
       </c>
       <c r="D329">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E329">
-        <v>38.987212500000005</v>
+        <v>43.32203684210527</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A330">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B330">
         <v>2018</v>
       </c>
       <c r="C330">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D330">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E330">
-        <v>38.121416666666654</v>
+        <v>42.589812500000008</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A331">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B331">
         <v>2018</v>
       </c>
       <c r="C331">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D331">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E331">
-        <v>40.494114583333342</v>
+        <v>41.960541176470585</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A332">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B332">
         <v>2018</v>
       </c>
       <c r="C332">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D332">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E332">
-        <v>41.521456250000007</v>
+        <v>41.050815909090907</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A333">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B333">
         <v>2018</v>
       </c>
       <c r="C333">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D333">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E333">
-        <v>41.320939583333335</v>
+        <v>39.999235416666671</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A334">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B334">
         <v>2018</v>
       </c>
       <c r="C334">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D334">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E334">
-        <v>40.903390909090916</v>
+        <v>39.066231250000008</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A335">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B335">
         <v>2018</v>
       </c>
       <c r="C335">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D335">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E335">
-        <v>41.556806249999994</v>
+        <v>41.981517499999988</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A336">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B336">
         <v>2018</v>
       </c>
       <c r="C336">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D336">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E336">
-        <v>41.487068749999985</v>
+        <v>41.82480833333333</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A337">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B337">
         <v>2018</v>
       </c>
       <c r="C337">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D337">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E337">
-        <v>40.106562499999995</v>
+        <v>41.156995833333333</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A338">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B338">
         <v>2018</v>
       </c>
       <c r="C338">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D338">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E338">
-        <v>40.912622916666663</v>
+        <v>40.488139583333336</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A339">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B339">
         <v>2018</v>
       </c>
       <c r="C339">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D339">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E339">
-        <v>41.050587499999999</v>
+        <v>39.788574999999994</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A340">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B340">
         <v>2018</v>
       </c>
       <c r="C340">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D340">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E340">
-        <v>41.461433333333332</v>
+        <v>39.633997916666658</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A341">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B341">
         <v>2018</v>
       </c>
       <c r="C341">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D341">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E341">
-        <v>41.316927083333333</v>
+        <v>39.808925000000002</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A342">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B342">
         <v>2018</v>
       </c>
       <c r="C342">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D342">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E342">
-        <v>42.214706249999999</v>
+        <v>39.024985416666667</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A343">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B343">
         <v>2018</v>
       </c>
       <c r="C343">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D343">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E343">
-        <v>41.724706250000004</v>
+        <v>38.122287499999992</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A344">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B344">
         <v>2018</v>
       </c>
       <c r="C344">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D344">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E344">
-        <v>40.550508333333326</v>
+        <v>37.540831249999989</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A345">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B345">
         <v>2018</v>
       </c>
       <c r="C345">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D345">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E345">
-        <v>39.657872499999996</v>
+        <v>36.611650000000004</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A346">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B346">
         <v>2018</v>
       </c>
       <c r="C346">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D346">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E346">
-        <v>39.038333333333334</v>
+        <v>35.42160208333334</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A347">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B347">
         <v>2018</v>
       </c>
       <c r="C347">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D347">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E347">
-        <v>39.737516666666664</v>
+        <v>34.16530208333333</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A348">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B348">
         <v>2018</v>
       </c>
       <c r="C348">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D348">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E348">
-        <v>39.826684210526317</v>
+        <v>32.812879166666669</v>
       </c>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A349">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B349">
         <v>2018</v>
       </c>
       <c r="C349">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D349">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E349">
-        <v>41.034704166666664</v>
+        <v>31.876722916666665</v>
       </c>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A350">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B350">
         <v>2018</v>
       </c>
       <c r="C350">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D350">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E350">
-        <v>41.426093750000007</v>
+        <v>31.026891666666671</v>
       </c>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A351">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B351">
         <v>2018</v>
@@ -9078,15 +6835,15 @@
         <v>7</v>
       </c>
       <c r="D351">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E351">
-        <v>40.133804166666678</v>
+        <v>30.523733333333329</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A352">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B352">
         <v>2018</v>
@@ -9095,15 +6852,15 @@
         <v>7</v>
       </c>
       <c r="D352">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E352">
-        <v>40.283127083333333</v>
+        <v>29.938385416666662</v>
       </c>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A353">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B353">
         <v>2018</v>
@@ -9112,15 +6869,15 @@
         <v>7</v>
       </c>
       <c r="D353">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E353">
-        <v>40.736441666666671</v>
+        <v>29.378872916666669</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A354">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B354">
         <v>2018</v>
@@ -9129,15 +6886,15 @@
         <v>7</v>
       </c>
       <c r="D354">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E354">
-        <v>39.704927083333331</v>
+        <v>28.928956249999999</v>
       </c>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A355">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B355">
         <v>2018</v>
@@ -9146,15 +6903,15 @@
         <v>7</v>
       </c>
       <c r="D355">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E355">
-        <v>38.572920833333335</v>
+        <v>28.744836956521741</v>
       </c>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A356">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B356">
         <v>2018</v>
@@ -9163,15 +6920,15 @@
         <v>7</v>
       </c>
       <c r="D356">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E356">
-        <v>36.853506250000002</v>
+        <v>28.536372916666668</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A357">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B357">
         <v>2018</v>
@@ -9180,15 +6937,15 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E357">
-        <v>34.042012499999991</v>
+        <v>28.116564583333329</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A358">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B358">
         <v>2018</v>
@@ -9197,15 +6954,15 @@
         <v>7</v>
       </c>
       <c r="D358">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E358">
-        <v>31.083460416666668</v>
+        <v>27.666866666666674</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A359">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B359">
         <v>2018</v>
@@ -9214,15 +6971,15 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E359">
-        <v>28.825729166666665</v>
+        <v>27.194014583333331</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A360">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B360">
         <v>2018</v>
@@ -9231,95 +6988,95 @@
         <v>7</v>
       </c>
       <c r="D360">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E360">
-        <v>27.386275000000001</v>
+        <v>26.823718750000001</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A361">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B361">
         <v>2018</v>
       </c>
       <c r="C361">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D361">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E361">
-        <v>26.241041666666661</v>
+        <v>26.598405555555559</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A362">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B362">
         <v>2018</v>
       </c>
       <c r="C362">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D362">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E362">
-        <v>25.3863375</v>
+        <v>26.488768750000002</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A363">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B363">
         <v>2018</v>
       </c>
       <c r="C363">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D363">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E363">
-        <v>24.923489583333335</v>
+        <v>26.512947916666665</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A364">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B364">
         <v>2018</v>
       </c>
       <c r="C364">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D364">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E364">
-        <v>24.503662500000001</v>
+        <v>26.446662499999999</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A365">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B365">
         <v>2018</v>
       </c>
       <c r="C365">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D365">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E365">
-        <v>24.220284090909093</v>
+        <v>26.306608333333333</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9330,13 +7087,13 @@
         <v>2018</v>
       </c>
       <c r="C366">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D366">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E366">
-        <v>41.510972222222222</v>
+        <v>26.141222499999998</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9347,13 +7104,13 @@
         <v>2018</v>
       </c>
       <c r="C367">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D367">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E367">
-        <v>41.959254166666661</v>
+        <v>25.785920833333336</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9364,13 +7121,13 @@
         <v>2018</v>
       </c>
       <c r="C368">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D368">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E368">
-        <v>42.261266666666664</v>
+        <v>25.383822916666663</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9381,13 +7138,13 @@
         <v>2018</v>
       </c>
       <c r="C369">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D369">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E369">
-        <v>42.507412500000001</v>
+        <v>25.217963157894733</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9398,13 +7155,13 @@
         <v>2018</v>
       </c>
       <c r="C370">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D370">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E370">
-        <v>42.257554166666665</v>
+        <v>25.157114583333339</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9415,13 +7172,13 @@
         <v>2018</v>
       </c>
       <c r="C371">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D371">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E371">
-        <v>41.507310416666662</v>
+        <v>25.159252083333339</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9432,13 +7189,13 @@
         <v>2018</v>
       </c>
       <c r="C372">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D372">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E372">
-        <v>41.504774999999988</v>
+        <v>25.167777083333334</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9449,13 +7206,13 @@
         <v>2018</v>
       </c>
       <c r="C373">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D373">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E373">
-        <v>41.831006249999994</v>
+        <v>25.159293478260871</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9466,13 +7223,13 @@
         <v>2018</v>
       </c>
       <c r="C374">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D374">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E374">
-        <v>42.062902083333334</v>
+        <v>24.671093749999997</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9483,13 +7240,13 @@
         <v>2018</v>
       </c>
       <c r="C375">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D375">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E375">
-        <v>42.12088541666666</v>
+        <v>24.390345833333338</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9500,13 +7257,13 @@
         <v>2018</v>
       </c>
       <c r="C376">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D376">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E376">
-        <v>42.116454166666678</v>
+        <v>24.298504166666664</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9517,13 +7274,13 @@
         <v>2018</v>
       </c>
       <c r="C377">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D377">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E377">
-        <v>41.68831458333333</v>
+        <v>24.33663125</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9534,13 +7291,13 @@
         <v>2018</v>
       </c>
       <c r="C378">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D378">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E378">
-        <v>41.494635714285714</v>
+        <v>24.409877083333328</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9551,13 +7308,13 @@
         <v>2018</v>
       </c>
       <c r="C379">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D379">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E379">
-        <v>42.487021428571431</v>
+        <v>24.529449999999997</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9568,13 +7325,13 @@
         <v>2018</v>
       </c>
       <c r="C380">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D380">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E380">
-        <v>42.729029166666663</v>
+        <v>24.511927083333337</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9585,13 +7342,13 @@
         <v>2018</v>
       </c>
       <c r="C381">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D381">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E381">
-        <v>42.974843750000012</v>
+        <v>24.478690909090911</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9602,13 +7359,13 @@
         <v>2018</v>
       </c>
       <c r="C382">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D382">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E382">
-        <v>43.361562499999991</v>
+        <v>24.439062500000002</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9619,13 +7376,13 @@
         <v>2018</v>
       </c>
       <c r="C383">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D383">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E383">
-        <v>43.530752380952379</v>
+        <v>24.387152083333334</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9636,13 +7393,13 @@
         <v>2018</v>
       </c>
       <c r="C384">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D384">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E384">
-        <v>43.693214285714284</v>
+        <v>24.336649999999995</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9653,13 +7410,13 @@
         <v>2018</v>
       </c>
       <c r="C385">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D385">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E385">
-        <v>43.472710714285711</v>
+        <v>24.247795833333331</v>
       </c>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -9670,1140 +7427,17 @@
         <v>2018</v>
       </c>
       <c r="C386">
+        <v>8</v>
+      </c>
+      <c r="D386">
         <v>5</v>
       </c>
-      <c r="D386">
-        <v>31</v>
-      </c>
       <c r="E386">
-        <v>43.174980000000005</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A387">
-        <v>29</v>
-      </c>
-      <c r="B387">
-        <v>2018</v>
-      </c>
-      <c r="C387">
-        <v>6</v>
-      </c>
-      <c r="D387">
-        <v>1</v>
-      </c>
-      <c r="E387">
-        <v>42.811390476190475</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A388">
-        <v>29</v>
-      </c>
-      <c r="B388">
-        <v>2018</v>
-      </c>
-      <c r="C388">
-        <v>6</v>
-      </c>
-      <c r="D388">
-        <v>2</v>
-      </c>
-      <c r="E388">
-        <v>42.446414999999995</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A389">
-        <v>29</v>
-      </c>
-      <c r="B389">
-        <v>2018</v>
-      </c>
-      <c r="C389">
-        <v>6</v>
-      </c>
-      <c r="D389">
-        <v>3</v>
-      </c>
-      <c r="E389">
-        <v>41.877272500000004</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A390">
-        <v>29</v>
-      </c>
-      <c r="B390">
-        <v>2018</v>
-      </c>
-      <c r="C390">
-        <v>6</v>
-      </c>
-      <c r="D390">
-        <v>4</v>
-      </c>
-      <c r="E390">
-        <v>41.083562500000006</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A391">
-        <v>29</v>
-      </c>
-      <c r="B391">
-        <v>2018</v>
-      </c>
-      <c r="C391">
-        <v>6</v>
-      </c>
-      <c r="D391">
-        <v>5</v>
-      </c>
-      <c r="E391">
-        <v>39.908275000000003</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A392">
-        <v>29</v>
-      </c>
-      <c r="B392">
-        <v>2018</v>
-      </c>
-      <c r="C392">
-        <v>6</v>
-      </c>
-      <c r="D392">
-        <v>6</v>
-      </c>
-      <c r="E392">
-        <v>38.772549999999995</v>
-      </c>
-    </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A393">
-        <v>29</v>
-      </c>
-      <c r="B393">
-        <v>2018</v>
-      </c>
-      <c r="C393">
-        <v>6</v>
-      </c>
-      <c r="D393">
-        <v>7</v>
-      </c>
-      <c r="E393">
-        <v>37.392376470588232</v>
-      </c>
-    </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A394">
-        <v>29</v>
-      </c>
-      <c r="B394">
-        <v>2018</v>
-      </c>
-      <c r="C394">
-        <v>6</v>
-      </c>
-      <c r="D394">
-        <v>8</v>
-      </c>
-      <c r="E394">
-        <v>37.843442105263158</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A395">
-        <v>29</v>
-      </c>
-      <c r="B395">
-        <v>2018</v>
-      </c>
-      <c r="C395">
-        <v>6</v>
-      </c>
-      <c r="D395">
-        <v>9</v>
-      </c>
-      <c r="E395">
-        <v>43.32203684210527</v>
-      </c>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A396">
-        <v>29</v>
-      </c>
-      <c r="B396">
-        <v>2018</v>
-      </c>
-      <c r="C396">
-        <v>6</v>
-      </c>
-      <c r="D396">
-        <v>10</v>
-      </c>
-      <c r="E396">
-        <v>42.589812500000008</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A397">
-        <v>29</v>
-      </c>
-      <c r="B397">
-        <v>2018</v>
-      </c>
-      <c r="C397">
-        <v>6</v>
-      </c>
-      <c r="D397">
-        <v>11</v>
-      </c>
-      <c r="E397">
-        <v>41.960541176470585</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A398">
-        <v>29</v>
-      </c>
-      <c r="B398">
-        <v>2018</v>
-      </c>
-      <c r="C398">
-        <v>6</v>
-      </c>
-      <c r="D398">
-        <v>12</v>
-      </c>
-      <c r="E398">
-        <v>41.050815909090907</v>
-      </c>
-    </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A399">
-        <v>29</v>
-      </c>
-      <c r="B399">
-        <v>2018</v>
-      </c>
-      <c r="C399">
-        <v>6</v>
-      </c>
-      <c r="D399">
-        <v>13</v>
-      </c>
-      <c r="E399">
-        <v>39.999235416666671</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A400">
-        <v>29</v>
-      </c>
-      <c r="B400">
-        <v>2018</v>
-      </c>
-      <c r="C400">
-        <v>6</v>
-      </c>
-      <c r="D400">
-        <v>14</v>
-      </c>
-      <c r="E400">
-        <v>39.066231250000008</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A401">
-        <v>29</v>
-      </c>
-      <c r="B401">
-        <v>2018</v>
-      </c>
-      <c r="C401">
-        <v>6</v>
-      </c>
-      <c r="D401">
-        <v>15</v>
-      </c>
-      <c r="E401">
-        <v>41.981517499999988</v>
-      </c>
-    </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A402">
-        <v>29</v>
-      </c>
-      <c r="B402">
-        <v>2018</v>
-      </c>
-      <c r="C402">
-        <v>6</v>
-      </c>
-      <c r="D402">
-        <v>16</v>
-      </c>
-      <c r="E402">
-        <v>41.82480833333333</v>
-      </c>
-    </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A403">
-        <v>29</v>
-      </c>
-      <c r="B403">
-        <v>2018</v>
-      </c>
-      <c r="C403">
-        <v>6</v>
-      </c>
-      <c r="D403">
-        <v>17</v>
-      </c>
-      <c r="E403">
-        <v>41.156995833333333</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A404">
-        <v>29</v>
-      </c>
-      <c r="B404">
-        <v>2018</v>
-      </c>
-      <c r="C404">
-        <v>6</v>
-      </c>
-      <c r="D404">
-        <v>18</v>
-      </c>
-      <c r="E404">
-        <v>40.488139583333336</v>
-      </c>
-    </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A405">
-        <v>29</v>
-      </c>
-      <c r="B405">
-        <v>2018</v>
-      </c>
-      <c r="C405">
-        <v>6</v>
-      </c>
-      <c r="D405">
-        <v>19</v>
-      </c>
-      <c r="E405">
-        <v>39.788574999999994</v>
-      </c>
-    </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A406">
-        <v>29</v>
-      </c>
-      <c r="B406">
-        <v>2018</v>
-      </c>
-      <c r="C406">
-        <v>6</v>
-      </c>
-      <c r="D406">
-        <v>20</v>
-      </c>
-      <c r="E406">
-        <v>39.633997916666658</v>
-      </c>
-    </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A407">
-        <v>29</v>
-      </c>
-      <c r="B407">
-        <v>2018</v>
-      </c>
-      <c r="C407">
-        <v>6</v>
-      </c>
-      <c r="D407">
-        <v>21</v>
-      </c>
-      <c r="E407">
-        <v>39.808925000000002</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A408">
-        <v>29</v>
-      </c>
-      <c r="B408">
-        <v>2018</v>
-      </c>
-      <c r="C408">
-        <v>6</v>
-      </c>
-      <c r="D408">
-        <v>22</v>
-      </c>
-      <c r="E408">
-        <v>39.024985416666667</v>
-      </c>
-    </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A409">
-        <v>29</v>
-      </c>
-      <c r="B409">
-        <v>2018</v>
-      </c>
-      <c r="C409">
-        <v>6</v>
-      </c>
-      <c r="D409">
-        <v>23</v>
-      </c>
-      <c r="E409">
-        <v>38.122287499999992</v>
-      </c>
-    </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A410">
-        <v>29</v>
-      </c>
-      <c r="B410">
-        <v>2018</v>
-      </c>
-      <c r="C410">
-        <v>6</v>
-      </c>
-      <c r="D410">
-        <v>24</v>
-      </c>
-      <c r="E410">
-        <v>37.540831249999989</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A411">
-        <v>29</v>
-      </c>
-      <c r="B411">
-        <v>2018</v>
-      </c>
-      <c r="C411">
-        <v>6</v>
-      </c>
-      <c r="D411">
-        <v>25</v>
-      </c>
-      <c r="E411">
-        <v>36.611650000000004</v>
-      </c>
-    </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A412">
-        <v>29</v>
-      </c>
-      <c r="B412">
-        <v>2018</v>
-      </c>
-      <c r="C412">
-        <v>6</v>
-      </c>
-      <c r="D412">
-        <v>26</v>
-      </c>
-      <c r="E412">
-        <v>35.42160208333334</v>
-      </c>
-    </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A413">
-        <v>29</v>
-      </c>
-      <c r="B413">
-        <v>2018</v>
-      </c>
-      <c r="C413">
-        <v>6</v>
-      </c>
-      <c r="D413">
-        <v>27</v>
-      </c>
-      <c r="E413">
-        <v>34.16530208333333</v>
-      </c>
-    </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A414">
-        <v>29</v>
-      </c>
-      <c r="B414">
-        <v>2018</v>
-      </c>
-      <c r="C414">
-        <v>6</v>
-      </c>
-      <c r="D414">
-        <v>28</v>
-      </c>
-      <c r="E414">
-        <v>32.812879166666669</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A415">
-        <v>29</v>
-      </c>
-      <c r="B415">
-        <v>2018</v>
-      </c>
-      <c r="C415">
-        <v>6</v>
-      </c>
-      <c r="D415">
-        <v>29</v>
-      </c>
-      <c r="E415">
-        <v>31.876722916666665</v>
-      </c>
-    </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A416">
-        <v>29</v>
-      </c>
-      <c r="B416">
-        <v>2018</v>
-      </c>
-      <c r="C416">
-        <v>6</v>
-      </c>
-      <c r="D416">
-        <v>30</v>
-      </c>
-      <c r="E416">
-        <v>31.026891666666671</v>
-      </c>
-    </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A417">
-        <v>29</v>
-      </c>
-      <c r="B417">
-        <v>2018</v>
-      </c>
-      <c r="C417">
-        <v>7</v>
-      </c>
-      <c r="D417">
-        <v>1</v>
-      </c>
-      <c r="E417">
-        <v>30.523733333333329</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A418">
-        <v>29</v>
-      </c>
-      <c r="B418">
-        <v>2018</v>
-      </c>
-      <c r="C418">
-        <v>7</v>
-      </c>
-      <c r="D418">
-        <v>2</v>
-      </c>
-      <c r="E418">
-        <v>29.938385416666662</v>
-      </c>
-    </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A419">
-        <v>29</v>
-      </c>
-      <c r="B419">
-        <v>2018</v>
-      </c>
-      <c r="C419">
-        <v>7</v>
-      </c>
-      <c r="D419">
-        <v>3</v>
-      </c>
-      <c r="E419">
-        <v>29.378872916666669</v>
-      </c>
-    </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A420">
-        <v>29</v>
-      </c>
-      <c r="B420">
-        <v>2018</v>
-      </c>
-      <c r="C420">
-        <v>7</v>
-      </c>
-      <c r="D420">
-        <v>4</v>
-      </c>
-      <c r="E420">
-        <v>28.928956249999999</v>
-      </c>
-    </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A421">
-        <v>29</v>
-      </c>
-      <c r="B421">
-        <v>2018</v>
-      </c>
-      <c r="C421">
-        <v>7</v>
-      </c>
-      <c r="D421">
-        <v>5</v>
-      </c>
-      <c r="E421">
-        <v>28.744836956521741</v>
-      </c>
-    </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A422">
-        <v>29</v>
-      </c>
-      <c r="B422">
-        <v>2018</v>
-      </c>
-      <c r="C422">
-        <v>7</v>
-      </c>
-      <c r="D422">
-        <v>6</v>
-      </c>
-      <c r="E422">
-        <v>28.536372916666668</v>
-      </c>
-    </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A423">
-        <v>29</v>
-      </c>
-      <c r="B423">
-        <v>2018</v>
-      </c>
-      <c r="C423">
-        <v>7</v>
-      </c>
-      <c r="D423">
-        <v>7</v>
-      </c>
-      <c r="E423">
-        <v>28.116564583333329</v>
-      </c>
-    </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A424">
-        <v>29</v>
-      </c>
-      <c r="B424">
-        <v>2018</v>
-      </c>
-      <c r="C424">
-        <v>7</v>
-      </c>
-      <c r="D424">
-        <v>8</v>
-      </c>
-      <c r="E424">
-        <v>27.666866666666674</v>
-      </c>
-    </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A425">
-        <v>29</v>
-      </c>
-      <c r="B425">
-        <v>2018</v>
-      </c>
-      <c r="C425">
-        <v>7</v>
-      </c>
-      <c r="D425">
-        <v>9</v>
-      </c>
-      <c r="E425">
-        <v>27.194014583333331</v>
-      </c>
-    </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A426">
-        <v>29</v>
-      </c>
-      <c r="B426">
-        <v>2018</v>
-      </c>
-      <c r="C426">
-        <v>7</v>
-      </c>
-      <c r="D426">
-        <v>10</v>
-      </c>
-      <c r="E426">
-        <v>26.823718750000001</v>
-      </c>
-    </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A427">
-        <v>29</v>
-      </c>
-      <c r="B427">
-        <v>2018</v>
-      </c>
-      <c r="C427">
-        <v>7</v>
-      </c>
-      <c r="D427">
-        <v>11</v>
-      </c>
-      <c r="E427">
-        <v>26.598405555555559</v>
-      </c>
-    </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A428">
-        <v>29</v>
-      </c>
-      <c r="B428">
-        <v>2018</v>
-      </c>
-      <c r="C428">
-        <v>7</v>
-      </c>
-      <c r="D428">
-        <v>12</v>
-      </c>
-      <c r="E428">
-        <v>26.488768750000002</v>
-      </c>
-    </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A429">
-        <v>29</v>
-      </c>
-      <c r="B429">
-        <v>2018</v>
-      </c>
-      <c r="C429">
-        <v>7</v>
-      </c>
-      <c r="D429">
-        <v>13</v>
-      </c>
-      <c r="E429">
-        <v>26.512947916666665</v>
-      </c>
-    </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A430">
-        <v>29</v>
-      </c>
-      <c r="B430">
-        <v>2018</v>
-      </c>
-      <c r="C430">
-        <v>7</v>
-      </c>
-      <c r="D430">
-        <v>14</v>
-      </c>
-      <c r="E430">
-        <v>26.446662499999999</v>
-      </c>
-    </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A431">
-        <v>29</v>
-      </c>
-      <c r="B431">
-        <v>2018</v>
-      </c>
-      <c r="C431">
-        <v>7</v>
-      </c>
-      <c r="D431">
-        <v>15</v>
-      </c>
-      <c r="E431">
-        <v>26.306608333333333</v>
-      </c>
-    </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A432">
-        <v>29</v>
-      </c>
-      <c r="B432">
-        <v>2018</v>
-      </c>
-      <c r="C432">
-        <v>7</v>
-      </c>
-      <c r="D432">
-        <v>16</v>
-      </c>
-      <c r="E432">
-        <v>26.141222499999998</v>
-      </c>
-    </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A433">
-        <v>29</v>
-      </c>
-      <c r="B433">
-        <v>2018</v>
-      </c>
-      <c r="C433">
-        <v>7</v>
-      </c>
-      <c r="D433">
-        <v>17</v>
-      </c>
-      <c r="E433">
-        <v>25.785920833333336</v>
-      </c>
-    </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A434">
-        <v>29</v>
-      </c>
-      <c r="B434">
-        <v>2018</v>
-      </c>
-      <c r="C434">
-        <v>7</v>
-      </c>
-      <c r="D434">
-        <v>18</v>
-      </c>
-      <c r="E434">
-        <v>25.383822916666663</v>
-      </c>
-    </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A435">
-        <v>29</v>
-      </c>
-      <c r="B435">
-        <v>2018</v>
-      </c>
-      <c r="C435">
-        <v>7</v>
-      </c>
-      <c r="D435">
-        <v>19</v>
-      </c>
-      <c r="E435">
-        <v>25.217963157894733</v>
-      </c>
-    </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A436">
-        <v>29</v>
-      </c>
-      <c r="B436">
-        <v>2018</v>
-      </c>
-      <c r="C436">
-        <v>7</v>
-      </c>
-      <c r="D436">
-        <v>20</v>
-      </c>
-      <c r="E436">
-        <v>25.157114583333339</v>
-      </c>
-    </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A437">
-        <v>29</v>
-      </c>
-      <c r="B437">
-        <v>2018</v>
-      </c>
-      <c r="C437">
-        <v>7</v>
-      </c>
-      <c r="D437">
-        <v>21</v>
-      </c>
-      <c r="E437">
-        <v>25.159252083333339</v>
-      </c>
-    </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A438">
-        <v>29</v>
-      </c>
-      <c r="B438">
-        <v>2018</v>
-      </c>
-      <c r="C438">
-        <v>7</v>
-      </c>
-      <c r="D438">
-        <v>22</v>
-      </c>
-      <c r="E438">
-        <v>25.167777083333334</v>
-      </c>
-    </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A439">
-        <v>29</v>
-      </c>
-      <c r="B439">
-        <v>2018</v>
-      </c>
-      <c r="C439">
-        <v>7</v>
-      </c>
-      <c r="D439">
-        <v>23</v>
-      </c>
-      <c r="E439">
-        <v>25.159293478260871</v>
-      </c>
-    </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A440">
-        <v>29</v>
-      </c>
-      <c r="B440">
-        <v>2018</v>
-      </c>
-      <c r="C440">
-        <v>7</v>
-      </c>
-      <c r="D440">
-        <v>24</v>
-      </c>
-      <c r="E440">
-        <v>24.671093749999997</v>
-      </c>
-    </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A441">
-        <v>29</v>
-      </c>
-      <c r="B441">
-        <v>2018</v>
-      </c>
-      <c r="C441">
-        <v>7</v>
-      </c>
-      <c r="D441">
-        <v>25</v>
-      </c>
-      <c r="E441">
-        <v>24.390345833333338</v>
-      </c>
-    </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A442">
-        <v>29</v>
-      </c>
-      <c r="B442">
-        <v>2018</v>
-      </c>
-      <c r="C442">
-        <v>7</v>
-      </c>
-      <c r="D442">
-        <v>26</v>
-      </c>
-      <c r="E442">
-        <v>24.298504166666664</v>
-      </c>
-    </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A443">
-        <v>29</v>
-      </c>
-      <c r="B443">
-        <v>2018</v>
-      </c>
-      <c r="C443">
-        <v>7</v>
-      </c>
-      <c r="D443">
-        <v>27</v>
-      </c>
-      <c r="E443">
-        <v>24.33663125</v>
-      </c>
-    </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A444">
-        <v>29</v>
-      </c>
-      <c r="B444">
-        <v>2018</v>
-      </c>
-      <c r="C444">
-        <v>7</v>
-      </c>
-      <c r="D444">
-        <v>28</v>
-      </c>
-      <c r="E444">
-        <v>24.409877083333328</v>
-      </c>
-    </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A445">
-        <v>29</v>
-      </c>
-      <c r="B445">
-        <v>2018</v>
-      </c>
-      <c r="C445">
-        <v>7</v>
-      </c>
-      <c r="D445">
-        <v>29</v>
-      </c>
-      <c r="E445">
-        <v>24.529449999999997</v>
-      </c>
-    </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A446">
-        <v>29</v>
-      </c>
-      <c r="B446">
-        <v>2018</v>
-      </c>
-      <c r="C446">
-        <v>7</v>
-      </c>
-      <c r="D446">
-        <v>30</v>
-      </c>
-      <c r="E446">
-        <v>24.511927083333337</v>
-      </c>
-    </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A447">
-        <v>29</v>
-      </c>
-      <c r="B447">
-        <v>2018</v>
-      </c>
-      <c r="C447">
-        <v>7</v>
-      </c>
-      <c r="D447">
-        <v>31</v>
-      </c>
-      <c r="E447">
-        <v>24.478690909090911</v>
-      </c>
-    </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A448">
-        <v>29</v>
-      </c>
-      <c r="B448">
-        <v>2018</v>
-      </c>
-      <c r="C448">
-        <v>8</v>
-      </c>
-      <c r="D448">
-        <v>1</v>
-      </c>
-      <c r="E448">
-        <v>24.439062500000002</v>
-      </c>
-    </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A449">
-        <v>29</v>
-      </c>
-      <c r="B449">
-        <v>2018</v>
-      </c>
-      <c r="C449">
-        <v>8</v>
-      </c>
-      <c r="D449">
-        <v>2</v>
-      </c>
-      <c r="E449">
-        <v>24.387152083333334</v>
-      </c>
-    </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A450">
-        <v>29</v>
-      </c>
-      <c r="B450">
-        <v>2018</v>
-      </c>
-      <c r="C450">
-        <v>8</v>
-      </c>
-      <c r="D450">
-        <v>3</v>
-      </c>
-      <c r="E450">
-        <v>24.336649999999995</v>
-      </c>
-    </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A451">
-        <v>29</v>
-      </c>
-      <c r="B451">
-        <v>2018</v>
-      </c>
-      <c r="C451">
-        <v>8</v>
-      </c>
-      <c r="D451">
-        <v>4</v>
-      </c>
-      <c r="E451">
-        <v>24.247795833333331</v>
-      </c>
-    </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A452">
-        <v>29</v>
-      </c>
-      <c r="B452">
-        <v>2018</v>
-      </c>
-      <c r="C452">
-        <v>8</v>
-      </c>
-      <c r="D452">
-        <v>5</v>
-      </c>
-      <c r="E452">
         <v>24.150681818181816</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
